--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid ABRA\Documents\UiPath\LRE Automation Performer\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpa.lre.res.dev\Documents\UiPath\PerformerProjet1LRE\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4930EFA-7A21-418B-B13B-1F5795B8CF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12705" yWindow="0" windowWidth="12975" windowHeight="15375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
   <si>
     <t>Name</t>
   </si>
@@ -156,9 +155,6 @@
     <t xml:space="preserve">The maximum number of consecutive system exceptions was reached. </t>
   </si>
   <si>
-    <t>FilesPDF</t>
-  </si>
-  <si>
     <t>LREProjet</t>
   </si>
   <si>
@@ -175,12 +171,48 @@
   </si>
   <si>
     <t>folderPathTraites</t>
+  </si>
+  <si>
+    <t>SGFD/LRE-RES</t>
+  </si>
+  <si>
+    <t>Chemin du dossier contenant les fichiers PDF en entrée</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chemin du dossier où seront stockés les fichiers que le robot ne pourra pas traiter</t>
+  </si>
+  <si>
+    <t>Chemin du dossier où seront stockés les fichiers traités par le robot</t>
+  </si>
+  <si>
+    <t>Chemin du dossier réseau de destination pour le fichier ZIP généré et le XML de consolidation.</t>
+  </si>
+  <si>
+    <t>Chemin du dossier ou se traite le dossier en cours</t>
+  </si>
+  <si>
+    <t>pdfQueue</t>
+  </si>
+  <si>
+    <t>DossierEncours</t>
+  </si>
+  <si>
+    <t>DossierRejet</t>
+  </si>
+  <si>
+    <t>DossierEntree</t>
+  </si>
+  <si>
+    <t>DossierTraitees</t>
+  </si>
+  <si>
+    <t>DossierSortie</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -549,14 +581,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.54296875" customWidth="1"/>
+    <col min="1" max="1" width="43.5703125" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="81.453125" customWidth="1"/>
-    <col min="4" max="26" width="8.6328125" customWidth="1"/>
+    <col min="3" max="3" width="81.42578125" customWidth="1"/>
+    <col min="4" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -598,28 +630,30 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="43.5">
+    <row r="3" spans="1:26" ht="45">
       <c r="A3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="29">
+    <row r="5" spans="1:26" ht="30">
       <c r="A5" t="s">
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>22</v>
@@ -1626,14 +1660,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z988"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="75.453125" customWidth="1"/>
-    <col min="4" max="26" width="8.6328125" customWidth="1"/>
+    <col min="3" max="3" width="75.42578125" customWidth="1"/>
+    <col min="4" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -1670,7 +1704,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="29">
+    <row r="2" spans="1:26" ht="30">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1681,7 +1715,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="43.5">
+    <row r="3" spans="1:26" ht="45">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -1795,7 +1829,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" spans="1:3" ht="29">
+    <row r="17" spans="1:3" ht="45">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -2784,14 +2818,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.90625" customWidth="1"/>
-    <col min="2" max="2" width="30.08984375" customWidth="1"/>
-    <col min="3" max="3" width="60.36328125" customWidth="1"/>
-    <col min="4" max="26" width="65.453125" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="60.42578125" customWidth="1"/>
+    <col min="4" max="26" width="65.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -2832,42 +2866,72 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>49</v>
+      <c r="D6" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpa.lre.res.dev\Documents\UiPath\PerformerProjet1LRE\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid ABRA\Documents\UiPath\LRE Automation Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4158E504-6C94-4DCC-8E96-5BDC84F7BF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12705" yWindow="0" windowWidth="12975" windowHeight="15375" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
   <si>
     <t>Name</t>
   </si>
@@ -207,12 +208,21 @@
   </si>
   <si>
     <t>DossierSortie</t>
+  </si>
+  <si>
+    <t>idDocument</t>
+  </si>
+  <si>
+    <t>idLot</t>
+  </si>
+  <si>
+    <t>DossierOrchestator</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -581,14 +591,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.5703125" customWidth="1"/>
+    <col min="1" max="1" width="43.54296875" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="81.42578125" customWidth="1"/>
-    <col min="4" max="26" width="8.5703125" customWidth="1"/>
+    <col min="3" max="3" width="81.453125" customWidth="1"/>
+    <col min="4" max="26" width="8.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -636,7 +646,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="43.5">
       <c r="A3" s="2" t="s">
         <v>30</v>
       </c>
@@ -648,7 +658,7 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="30">
+    <row r="5" spans="1:26" ht="29">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1660,14 +1670,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z988"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="75.42578125" customWidth="1"/>
-    <col min="4" max="26" width="8.5703125" customWidth="1"/>
+    <col min="3" max="3" width="75.453125" customWidth="1"/>
+    <col min="4" max="26" width="8.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -1704,7 +1714,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="30">
+    <row r="2" spans="1:26" ht="29">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1715,7 +1725,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="43.5">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -1829,7 +1839,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" spans="1:3" ht="45">
+    <row r="17" spans="1:3" ht="29">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -1840,9 +1850,30 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="19" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="18" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+    </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
@@ -2818,14 +2849,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Feuil1"/>
+  <dimension ref="A1:Z998"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="3" width="60.42578125" customWidth="1"/>
-    <col min="4" max="26" width="65.42578125" customWidth="1"/>
+    <col min="1" max="1" width="31.81640625" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" customWidth="1"/>
+    <col min="3" max="3" width="60.453125" customWidth="1"/>
+    <col min="4" max="26" width="65.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -2907,10 +2939,10 @@
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5" t="s">
@@ -2921,10 +2953,10 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>59</v>
       </c>
       <c r="C6" t="s">
@@ -3926,8 +3958,6 @@
     <row r="996" ht="14.25" customHeight="1"/>
     <row r="997" ht="14.25" customHeight="1"/>
     <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid ABRA\Documents\UiPath\LRE Automation Performer\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpa.lre.res.dev\Documents\UiPath\PerformerProjet1LRE\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4158E504-6C94-4DCC-8E96-5BDC84F7BF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5010" yWindow="1965" windowWidth="19200" windowHeight="11175" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
   <si>
     <t>Name</t>
   </si>
@@ -217,12 +216,24 @@
   </si>
   <si>
     <t>DossierOrchestator</t>
+  </si>
+  <si>
+    <t>in_pathReport</t>
+  </si>
+  <si>
+    <t>CheminRapport</t>
+  </si>
+  <si>
+    <t>folderReport</t>
+  </si>
+  <si>
+    <t>DossierRapport</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -591,14 +602,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.54296875" customWidth="1"/>
+    <col min="1" max="1" width="43.5703125" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="81.453125" customWidth="1"/>
-    <col min="4" max="26" width="8.54296875" customWidth="1"/>
+    <col min="3" max="3" width="81.42578125" customWidth="1"/>
+    <col min="4" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -646,7 +657,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="43.5">
+    <row r="3" spans="1:26" ht="45">
       <c r="A3" s="2" t="s">
         <v>30</v>
       </c>
@@ -658,7 +669,7 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="29">
+    <row r="5" spans="1:26" ht="30">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1670,14 +1681,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z988"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="75.453125" customWidth="1"/>
-    <col min="4" max="26" width="8.54296875" customWidth="1"/>
+    <col min="3" max="3" width="75.42578125" customWidth="1"/>
+    <col min="4" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -1714,7 +1725,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="29">
+    <row r="2" spans="1:26" ht="30">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1725,7 +1736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="43.5">
+    <row r="3" spans="1:26" ht="45">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -1839,7 +1850,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" spans="1:3" ht="29">
+    <row r="17" spans="1:3" ht="45">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -2849,15 +2860,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Feuil1"/>
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.81640625" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" customWidth="1"/>
-    <col min="3" max="3" width="60.453125" customWidth="1"/>
-    <col min="4" max="26" width="65.453125" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="60.42578125" customWidth="1"/>
+    <col min="4" max="26" width="65.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -2966,8 +2977,28 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+    </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpa.lre.res.dev\Documents\UiPath\PerformerProjet1LRE\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid ABRA\Documents\UiPath\LRE Automation Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{467BF6F5-631A-4A67-9D7E-4BA91191C379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="1965" windowWidth="19200" windowHeight="11175" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -233,7 +234,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -602,14 +603,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.5703125" customWidth="1"/>
+    <col min="1" max="1" width="43.54296875" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="81.42578125" customWidth="1"/>
-    <col min="4" max="26" width="8.5703125" customWidth="1"/>
+    <col min="3" max="3" width="81.453125" customWidth="1"/>
+    <col min="4" max="26" width="8.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -657,7 +658,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="43.5">
       <c r="A3" s="2" t="s">
         <v>30</v>
       </c>
@@ -669,7 +670,7 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="30">
+    <row r="5" spans="1:26" ht="29">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1681,14 +1682,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z988"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="75.42578125" customWidth="1"/>
-    <col min="4" max="26" width="8.5703125" customWidth="1"/>
+    <col min="3" max="3" width="75.453125" customWidth="1"/>
+    <col min="4" max="26" width="8.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -1725,7 +1726,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="30">
+    <row r="2" spans="1:26" ht="29">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1736,7 +1737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="43.5">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -1850,7 +1851,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" spans="1:3" ht="45">
+    <row r="17" spans="1:3" ht="29">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -2860,15 +2861,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Feuil1"/>
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="3" width="60.42578125" customWidth="1"/>
-    <col min="4" max="26" width="65.42578125" customWidth="1"/>
+    <col min="1" max="1" width="31.81640625" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" customWidth="1"/>
+    <col min="3" max="3" width="60.453125" customWidth="1"/>
+    <col min="4" max="26" width="65.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid ABRA\Documents\UiPath\PerformerProjet1LRE 2607\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F8B97D-090E-4CCF-82F5-283F3AEBCBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E7B11E-C0C0-4FF3-A9EA-6F40D52772F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1480" yWindow="1480" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="113">
   <si>
     <t>Name</t>
   </si>
@@ -316,6 +316,54 @@
   </si>
   <si>
     <t>Objet</t>
+  </si>
+  <si>
+    <t>BE008</t>
+  </si>
+  <si>
+    <t>Dossier introuvable</t>
+  </si>
+  <si>
+    <t>bodyBE001</t>
+  </si>
+  <si>
+    <t>bodyBE002</t>
+  </si>
+  <si>
+    <t>bodyBE003</t>
+  </si>
+  <si>
+    <t>bodyBE004</t>
+  </si>
+  <si>
+    <t>bodyBE005</t>
+  </si>
+  <si>
+    <t>bodyBE006</t>
+  </si>
+  <si>
+    <t>bodyBE007</t>
+  </si>
+  <si>
+    <t>bodyBE008</t>
+  </si>
+  <si>
+    <t>bodyBE011</t>
+  </si>
+  <si>
+    <t>bodyBE012</t>
+  </si>
+  <si>
+    <t>bodyBE013</t>
+  </si>
+  <si>
+    <t>bodyBE099</t>
+  </si>
+  <si>
+    <t>Erreur Inconnu</t>
+  </si>
+  <si>
+    <t>BE099</t>
   </si>
 </sst>
 </file>
@@ -347,12 +395,24 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -367,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -377,6 +437,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1973,34 +2036,125 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="24" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="25" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="26" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="27" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="29" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="30" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="31" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="32" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="21" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A21" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A22" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A23" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A24" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A25" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A26" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A27" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A28" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A29" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A30" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A31" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A32" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A33" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="35" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="36" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="37" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="38" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="39" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="40" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="41" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="42" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="43" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="44" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="45" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="46" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="47" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="48" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -2950,7 +3104,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Feuil1"/>
-  <dimension ref="A1:Z993"/>
+  <dimension ref="A1:Z994"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.81640625" customWidth="1"/>
@@ -3093,31 +3247,31 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A9" t="s">
+    <row r="9" spans="1:26" s="5" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A10" t="s">
+    <row r="10" spans="1:26" s="6" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A10" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="6" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3135,144 +3289,157 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A12" t="s">
+    <row r="12" spans="1:26" s="6" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" t="s">
+    <row r="13" spans="1:26" s="6" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A13" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A14" t="s">
+    <row r="14" spans="1:26" s="6" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A14" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A15" t="s">
+    <row r="15" spans="1:26" s="6" customFormat="1" ht="14" customHeight="1">
+      <c r="A15" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="16" spans="1:26" s="6" customFormat="1" ht="14" customHeight="1">
+      <c r="A16" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D16" t="s">
-        <v>90</v>
+      <c r="D16" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
         <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
         <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
         <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
         <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="14.25" customHeight="1"/>
+      <c r="D21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A22" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+    </row>
     <row r="23" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="24" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="25" spans="1:4" ht="14.25" customHeight="1"/>
@@ -4244,6 +4411,7 @@
     <row r="991" ht="14.25" customHeight="1"/>
     <row r="992" ht="14.25" customHeight="1"/>
     <row r="993" ht="14.25" customHeight="1"/>
+    <row r="994" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid ABRA\Documents\UiPath\PerformerProjet1LRE 2607\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E7B11E-C0C0-4FF3-A9EA-6F40D52772F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77BBFFE1-6ED0-42CA-A5A7-D260816EB22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1480" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="161">
   <si>
     <t>Name</t>
   </si>
@@ -207,15 +207,6 @@
     <t>DossierSortie</t>
   </si>
   <si>
-    <t>idDocument</t>
-  </si>
-  <si>
-    <t>idLot</t>
-  </si>
-  <si>
-    <t>DossierOrchestator</t>
-  </si>
-  <si>
     <t>folderReport</t>
   </si>
   <si>
@@ -360,10 +351,163 @@
     <t>bodyBE099</t>
   </si>
   <si>
-    <t>Erreur Inconnu</t>
-  </si>
-  <si>
     <t>BE099</t>
+  </si>
+  <si>
+    <t>BE001Corps</t>
+  </si>
+  <si>
+    <t>BE002Corps</t>
+  </si>
+  <si>
+    <t>BE003Corps</t>
+  </si>
+  <si>
+    <t>BE004Corps</t>
+  </si>
+  <si>
+    <t>BE005Corps</t>
+  </si>
+  <si>
+    <t>BE006Corps</t>
+  </si>
+  <si>
+    <t>BE007Corps</t>
+  </si>
+  <si>
+    <t>BE008Corps</t>
+  </si>
+  <si>
+    <t>BE011Corps</t>
+  </si>
+  <si>
+    <t>BE012Corps</t>
+  </si>
+  <si>
+    <t>BE013Corps</t>
+  </si>
+  <si>
+    <t>BE099Corps</t>
+  </si>
+  <si>
+    <t>objectBE001</t>
+  </si>
+  <si>
+    <t>objectBE002</t>
+  </si>
+  <si>
+    <t>objectBE003</t>
+  </si>
+  <si>
+    <t>objectBE004</t>
+  </si>
+  <si>
+    <t>objectBE005</t>
+  </si>
+  <si>
+    <t>objectBE006</t>
+  </si>
+  <si>
+    <t>objectBE007</t>
+  </si>
+  <si>
+    <t>objectBE008</t>
+  </si>
+  <si>
+    <t>objectBE011</t>
+  </si>
+  <si>
+    <t>objectBE012</t>
+  </si>
+  <si>
+    <t>objectBE013</t>
+  </si>
+  <si>
+    <t>BE001Objet</t>
+  </si>
+  <si>
+    <t>BE002Objet</t>
+  </si>
+  <si>
+    <t>BE003Objet</t>
+  </si>
+  <si>
+    <t>BE004Objet</t>
+  </si>
+  <si>
+    <t>BE005Objet</t>
+  </si>
+  <si>
+    <t>BE006Objet</t>
+  </si>
+  <si>
+    <t>BE007Objet</t>
+  </si>
+  <si>
+    <t>BE008Objet</t>
+  </si>
+  <si>
+    <t>BE011Objet</t>
+  </si>
+  <si>
+    <t>BE012Objet</t>
+  </si>
+  <si>
+    <t>BE013Objet</t>
+  </si>
+  <si>
+    <t>objectBE099</t>
+  </si>
+  <si>
+    <t>BE099Objet</t>
+  </si>
+  <si>
+    <t>Erreur Inconnue</t>
+  </si>
+  <si>
+    <t>NomRapportMensuel</t>
+  </si>
+  <si>
+    <t>NomRapportExecution</t>
+  </si>
+  <si>
+    <t>NomRapportRejet</t>
+  </si>
+  <si>
+    <t>NomRapportErreur</t>
+  </si>
+  <si>
+    <t>Feuille Rapport Execution</t>
+  </si>
+  <si>
+    <t>Feuille Rapport Mensuel</t>
+  </si>
+  <si>
+    <t>Feuille Rapport Rejet</t>
+  </si>
+  <si>
+    <t>Feuille Rapport Erreur</t>
+  </si>
+  <si>
+    <t>Domaine</t>
+  </si>
+  <si>
+    <t>MATMUTRPA</t>
+  </si>
+  <si>
+    <t>FeuilleRapport d'execution</t>
+  </si>
+  <si>
+    <t>Rapport Mensuel -</t>
+  </si>
+  <si>
+    <t>Rapport d'execution -</t>
+  </si>
+  <si>
+    <t>Rapport Rejet -</t>
+  </si>
+  <si>
+    <t>Rapport Erreur -</t>
   </si>
 </sst>
 </file>
@@ -395,24 +539,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -427,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -437,9 +569,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1833,7 +1962,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z988"/>
+  <dimension ref="A1:Z970"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -2014,147 +2143,98 @@
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>146</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A21" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>83</v>
+      <c r="A21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A22" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>84</v>
+      <c r="A22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B22" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A23" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>85</v>
+      <c r="A23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A24" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>86</v>
+      <c r="A24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A25" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>87</v>
+      <c r="A25" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A26" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A27" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A28" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A29" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A30" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A31" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A32" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A33" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="35" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="36" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="37" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="38" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="39" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="40" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="41" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="42" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="43" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="44" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="45" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="46" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="47" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="48" spans="1:2" ht="14.25" customHeight="1"/>
+      <c r="A26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="33" ht="14.25" customHeight="1"/>
+    <row r="34" ht="14.25" customHeight="1"/>
+    <row r="35" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="43" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
+    <row r="48" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -3077,24 +3157,6 @@
     <row r="968" ht="14.25" customHeight="1"/>
     <row r="969" ht="14.25" customHeight="1"/>
     <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3104,7 +3166,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Feuil1"/>
-  <dimension ref="A1:Z994"/>
+  <dimension ref="A1:Z995"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.81640625" customWidth="1"/>
@@ -3188,7 +3250,7 @@
         <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
@@ -3221,251 +3283,504 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
         <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
         <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" s="5" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" s="6" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="D9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>84</v>
+      <c r="D10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
         <v>49</v>
       </c>
       <c r="D11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:26" s="6" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A12" s="6" t="s">
+    <row r="15" spans="1:26" ht="14" customHeight="1">
+      <c r="A15" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B15" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C15" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D15" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:26" s="6" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="6" t="s">
+    <row r="16" spans="1:26" ht="14" customHeight="1">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" s="6" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A14" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" s="6" customFormat="1" ht="14" customHeight="1">
-      <c r="A15" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" s="6" customFormat="1" ht="14" customHeight="1">
-      <c r="A16" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>98</v>
+      <c r="D16" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
         <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
         <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
         <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A20" t="s">
-        <v>65</v>
+      <c r="A20" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
         <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
         <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="24" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="25" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="26" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="27" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="28" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="29" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="30" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="31" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="32" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
+      <c r="D22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A34" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A35" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A36" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A38" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A39" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A40" t="s">
+        <v>125</v>
+      </c>
+      <c r="B40" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A41" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A42" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A43" t="s">
+        <v>128</v>
+      </c>
+      <c r="B43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A44" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A45" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A46" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A47" t="s">
+        <v>143</v>
+      </c>
+      <c r="B47" t="s">
+        <v>144</v>
+      </c>
+      <c r="C47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -4412,6 +4727,7 @@
     <row r="992" ht="14.25" customHeight="1"/>
     <row r="993" ht="14.25" customHeight="1"/>
     <row r="994" ht="14.25" customHeight="1"/>
+    <row r="995" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid ABRA\Documents\UiPath\PerformerProjet1LRE 2607\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpa.lre.res.dev\Documents\UiPath\PerformerProjet1LRE\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77BBFFE1-6ED0-42CA-A5A7-D260816EB22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="13815"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="164">
   <si>
     <t>Name</t>
   </si>
@@ -498,23 +497,32 @@
     <t>FeuilleRapport d'execution</t>
   </si>
   <si>
-    <t>Rapport Mensuel -</t>
-  </si>
-  <si>
-    <t>Rapport d'execution -</t>
-  </si>
-  <si>
-    <t>Rapport Rejet -</t>
-  </si>
-  <si>
-    <t>Rapport Erreur -</t>
+    <t>Rapport Mensuel</t>
+  </si>
+  <si>
+    <t>Rapport d'execution</t>
+  </si>
+  <si>
+    <t>Rapport Rejet</t>
+  </si>
+  <si>
+    <t>Rapport Erreur</t>
+  </si>
+  <si>
+    <t>ProcessName</t>
+  </si>
+  <si>
+    <t>LRE Performer</t>
+  </si>
+  <si>
+    <t>wabra@silamir.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -538,6 +546,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -556,10 +570,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -569,8 +584,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -882,14 +899,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.54296875" customWidth="1"/>
+    <col min="1" max="1" width="43.5703125" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="81.453125" customWidth="1"/>
-    <col min="4" max="26" width="8.54296875" customWidth="1"/>
+    <col min="3" max="3" width="81.42578125" customWidth="1"/>
+    <col min="4" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -937,19 +954,17 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="43.5">
+    <row r="3" spans="1:26" ht="45">
       <c r="A3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="29">
+    <row r="5" spans="1:26" ht="30">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -961,7 +976,14 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" t="s">
+        <v>162</v>
+      </c>
+    </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
@@ -1961,14 +1983,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z970"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="75.453125" customWidth="1"/>
-    <col min="4" max="26" width="8.54296875" customWidth="1"/>
+    <col min="3" max="3" width="75.42578125" customWidth="1"/>
+    <col min="4" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -2005,18 +2027,18 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="29">
+    <row r="2" spans="1:26" ht="30">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="43.5">
+    <row r="3" spans="1:26" ht="45">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -2130,7 +2152,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" spans="1:3" ht="29">
+    <row r="17" spans="1:4" ht="45">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -2141,7 +2163,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="14.25" customHeight="1">
+    <row r="18" spans="1:4" ht="14.25" customHeight="1">
       <c r="A18" t="s">
         <v>146</v>
       </c>
@@ -2149,7 +2171,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="14.25" customHeight="1">
+    <row r="19" spans="1:4" ht="14.25" customHeight="1">
       <c r="A19" t="s">
         <v>147</v>
       </c>
@@ -2157,7 +2179,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="14.25" customHeight="1">
+    <row r="20" spans="1:4" ht="14.25" customHeight="1">
       <c r="A20" t="s">
         <v>148</v>
       </c>
@@ -2165,7 +2187,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="14.25" customHeight="1">
+    <row r="21" spans="1:4" ht="14.25" customHeight="1">
       <c r="A21" t="s">
         <v>149</v>
       </c>
@@ -2173,7 +2195,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="14.25" customHeight="1">
+    <row r="22" spans="1:4" ht="14.25" customHeight="1">
       <c r="A22" t="s">
         <v>151</v>
       </c>
@@ -2181,7 +2203,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="14.25" customHeight="1">
+    <row r="23" spans="1:4" ht="14.25" customHeight="1">
       <c r="A23" t="s">
         <v>150</v>
       </c>
@@ -2189,7 +2211,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="14.25" customHeight="1">
+    <row r="24" spans="1:4" ht="14.25" customHeight="1">
       <c r="A24" t="s">
         <v>152</v>
       </c>
@@ -2197,7 +2219,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="14.25" customHeight="1">
+    <row r="25" spans="1:4" ht="14.25" customHeight="1">
       <c r="A25" t="s">
         <v>153</v>
       </c>
@@ -2205,7 +2227,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="14.25" customHeight="1">
+    <row r="26" spans="1:4" ht="14.25" customHeight="1">
       <c r="A26" t="s">
         <v>154</v>
       </c>
@@ -2213,12 +2235,25 @@
         <v>155</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="29" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="30" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="31" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="32" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -3159,20 +3194,23 @@
     <row r="970" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Feuil1"/>
-  <dimension ref="A1:Z995"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Z994"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.81640625" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" customWidth="1"/>
-    <col min="4" max="26" width="65.453125" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" customWidth="1"/>
+    <col min="4" max="26" width="65.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -3393,7 +3431,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="14" customHeight="1">
+    <row r="15" spans="1:26" ht="14.1" customHeight="1">
       <c r="A15" t="s">
         <v>71</v>
       </c>
@@ -3407,7 +3445,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="14" customHeight="1">
+    <row r="16" spans="1:26" ht="14.1" customHeight="1">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -3479,38 +3517,35 @@
     </row>
     <row r="21" spans="1:4" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
         <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
         <v>49</v>
       </c>
-      <c r="D22" t="s">
-        <v>90</v>
-      </c>
     </row>
     <row r="23" spans="1:4" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
         <v>49</v>
@@ -3518,10 +3553,10 @@
     </row>
     <row r="24" spans="1:4" ht="14.25" customHeight="1">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
         <v>49</v>
@@ -3529,10 +3564,10 @@
     </row>
     <row r="25" spans="1:4" ht="14.25" customHeight="1">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
         <v>49</v>
@@ -3540,10 +3575,10 @@
     </row>
     <row r="26" spans="1:4" ht="14.25" customHeight="1">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
         <v>49</v>
@@ -3551,10 +3586,10 @@
     </row>
     <row r="27" spans="1:4" ht="14.25" customHeight="1">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
         <v>49</v>
@@ -3562,10 +3597,10 @@
     </row>
     <row r="28" spans="1:4" ht="14.25" customHeight="1">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
         <v>49</v>
@@ -3573,10 +3608,10 @@
     </row>
     <row r="29" spans="1:4" ht="14.25" customHeight="1">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
         <v>49</v>
@@ -3584,10 +3619,10 @@
     </row>
     <row r="30" spans="1:4" ht="14.25" customHeight="1">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
         <v>49</v>
@@ -3595,10 +3630,10 @@
     </row>
     <row r="31" spans="1:4" ht="14.25" customHeight="1">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s">
         <v>49</v>
@@ -3606,10 +3641,10 @@
     </row>
     <row r="32" spans="1:4" ht="14.25" customHeight="1">
       <c r="A32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s">
         <v>49</v>
@@ -3617,10 +3652,10 @@
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
         <v>49</v>
@@ -3628,10 +3663,10 @@
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1">
       <c r="A34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C34" t="s">
         <v>49</v>
@@ -3639,10 +3674,10 @@
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1">
       <c r="A35" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C35" t="s">
         <v>49</v>
@@ -3650,10 +3685,10 @@
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
         <v>49</v>
@@ -3661,10 +3696,10 @@
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C37" t="s">
         <v>49</v>
@@ -3672,10 +3707,10 @@
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
         <v>49</v>
@@ -3683,10 +3718,10 @@
     </row>
     <row r="39" spans="1:3" ht="14.25" customHeight="1">
       <c r="A39" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C39" t="s">
         <v>49</v>
@@ -3694,10 +3729,10 @@
     </row>
     <row r="40" spans="1:3" ht="14.25" customHeight="1">
       <c r="A40" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C40" t="s">
         <v>49</v>
@@ -3705,10 +3740,10 @@
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1">
       <c r="A41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
         <v>49</v>
@@ -3716,10 +3751,10 @@
     </row>
     <row r="42" spans="1:3" ht="14.25" customHeight="1">
       <c r="A42" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
         <v>49</v>
@@ -3727,10 +3762,10 @@
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1">
       <c r="A43" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C43" t="s">
         <v>49</v>
@@ -3738,10 +3773,10 @@
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1">
       <c r="A44" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C44" t="s">
         <v>49</v>
@@ -3749,10 +3784,10 @@
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1">
       <c r="A45" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C45" t="s">
         <v>49</v>
@@ -3760,26 +3795,16 @@
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1">
       <c r="A46" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C46" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A47" t="s">
-        <v>143</v>
-      </c>
-      <c r="B47" t="s">
-        <v>144</v>
-      </c>
-      <c r="C47" t="s">
-        <v>49</v>
-      </c>
-    </row>
+    <row r="47" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="48" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
@@ -4727,7 +4752,6 @@
     <row r="992" ht="14.25" customHeight="1"/>
     <row r="993" ht="14.25" customHeight="1"/>
     <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpa.lre.res.dev\Documents\UiPath\PerformerProjet1LRE\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid ABRA\Documents\UiPath\PerformerProjet1LRE\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FD107F-504D-46BE-A9E4-C156996EEEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="13815"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="38700" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="146">
   <si>
     <t>Name</t>
   </si>
@@ -176,51 +177,18 @@
     <t>SGFD/LRE-RES</t>
   </si>
   <si>
-    <t>Chemin du dossier contenant les fichiers PDF en entrée</t>
-  </si>
-  <si>
-    <t>Chemin du dossier où seront stockés les fichiers traités par le robot</t>
-  </si>
-  <si>
-    <t>Chemin du dossier réseau de destination pour le fichier ZIP généré et le XML de consolidation.</t>
-  </si>
-  <si>
-    <t>Chemin du dossier ou se traite le dossier en cours</t>
-  </si>
-  <si>
     <t>pdfQueue</t>
   </si>
   <si>
-    <t>DossierEncours</t>
-  </si>
-  <si>
-    <t>DossierRejet</t>
-  </si>
-  <si>
-    <t>DossierEntree</t>
-  </si>
-  <si>
-    <t>DossierTraitees</t>
-  </si>
-  <si>
-    <t>DossierSortie</t>
-  </si>
-  <si>
     <t>folderReport</t>
   </si>
   <si>
-    <t>DossierRapport</t>
-  </si>
-  <si>
     <t>Destinataire</t>
   </si>
   <si>
     <t>folderPathTmp</t>
   </si>
   <si>
-    <t>DossierTemporaire</t>
-  </si>
-  <si>
     <t>BE001</t>
   </si>
   <si>
@@ -251,54 +219,12 @@
     <t>BE013</t>
   </si>
   <si>
-    <t>Chemin du dossier où seront stockés les fichiers que le robot ne pourra pas traiter</t>
-  </si>
-  <si>
     <t>bodyMessage</t>
   </si>
   <si>
-    <t>Chemin du dossier où seront stockés les rapports</t>
-  </si>
-  <si>
     <t>Le destinataire du mail d'erreur</t>
   </si>
   <si>
-    <t>Chemin du dossier où seront stockés les fichiers qui seront zippé</t>
-  </si>
-  <si>
-    <t>Id ou MDP windows KO</t>
-  </si>
-  <si>
-    <t>Accès aux données d’entrées impossible</t>
-  </si>
-  <si>
-    <t>Données d’entrées absentes</t>
-  </si>
-  <si>
-    <t>Accès au template impossible</t>
-  </si>
-  <si>
-    <t>Excel KO</t>
-  </si>
-  <si>
-    <t>Accès au dossier pour le dépôt impossible</t>
-  </si>
-  <si>
-    <t>Outlook KO</t>
-  </si>
-  <si>
-    <t>Extraction KO/format KO</t>
-  </si>
-  <si>
-    <t>Hors périmètre</t>
-  </si>
-  <si>
-    <t>Existence de plusieurs réferences dans une seule page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LE corps du mail à envoyer au destinataire en cas d'erreur </t>
-  </si>
-  <si>
     <t>CorpsMail</t>
   </si>
   <si>
@@ -311,9 +237,6 @@
     <t>BE008</t>
   </si>
   <si>
-    <t>Dossier introuvable</t>
-  </si>
-  <si>
     <t>bodyBE001</t>
   </si>
   <si>
@@ -461,9 +384,6 @@
     <t>BE099Objet</t>
   </si>
   <si>
-    <t>Erreur Inconnue</t>
-  </si>
-  <si>
     <t>NomRapportMensuel</t>
   </si>
   <si>
@@ -516,12 +436,39 @@
   </si>
   <si>
     <t>wabra@silamir.com</t>
+  </si>
+  <si>
+    <t>motcle</t>
+  </si>
+  <si>
+    <t>Intercalaire</t>
+  </si>
+  <si>
+    <t>C:\Users\Walid ABRA\Documents\TEST\1</t>
+  </si>
+  <si>
+    <t>C:\Users\Walid ABRA\Documents\TEST\2</t>
+  </si>
+  <si>
+    <t>C:\Users\Walid ABRA\Documents\TEST\3</t>
+  </si>
+  <si>
+    <t>C:\Users\Walid ABRA\Documents\TEST\4</t>
+  </si>
+  <si>
+    <t>C:\Users\Walid ABRA\Documents\TEST\5</t>
+  </si>
+  <si>
+    <t>C:\Users\Walid ABRA\Documents\TEST\6</t>
+  </si>
+  <si>
+    <t>C:\Users\Walid ABRA\Documents\TEST\7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -899,7 +846,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z998"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -948,7 +895,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -978,10 +925,10 @@
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
@@ -1983,7 +1930,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z970"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -2165,95 +2112,1450 @@
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="B22" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="B23" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="14.25" customHeight="1">
       <c r="A24" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="B24" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="14.25" customHeight="1">
       <c r="A25" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="B25" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="14.25" customHeight="1">
       <c r="A26" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="B26" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="14.25" customHeight="1">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="C27" t="s">
         <v>49</v>
       </c>
       <c r="D27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A30" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A47" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A48" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A49" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A50" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A51" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A52" t="s">
+        <v>71</v>
+      </c>
+      <c r="B52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A53" t="s">
+        <v>72</v>
+      </c>
+      <c r="B53" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A54" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A55" t="s">
+        <v>74</v>
+      </c>
+      <c r="B55" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A56" t="s">
+        <v>75</v>
+      </c>
+      <c r="B56" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A57" t="s">
+        <v>76</v>
+      </c>
+      <c r="B57" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B58" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A59" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="29" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="30" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="31" spans="1:4" ht="14.25" customHeight="1"/>
-    <row r="32" spans="1:4" ht="14.25" customHeight="1"/>
+      <c r="B59" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A60" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A61" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A62" t="s">
+        <v>81</v>
+      </c>
+      <c r="B62" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A63" t="s">
+        <v>95</v>
+      </c>
+      <c r="B63" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A64" t="s">
+        <v>96</v>
+      </c>
+      <c r="B64" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A65" t="s">
+        <v>97</v>
+      </c>
+      <c r="B65" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A66" t="s">
+        <v>98</v>
+      </c>
+      <c r="B66" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A67" t="s">
+        <v>99</v>
+      </c>
+      <c r="B67" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A68" t="s">
+        <v>100</v>
+      </c>
+      <c r="B68" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A69" t="s">
+        <v>101</v>
+      </c>
+      <c r="B69" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A70" t="s">
+        <v>102</v>
+      </c>
+      <c r="B70" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A71" t="s">
+        <v>103</v>
+      </c>
+      <c r="B71" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A72" t="s">
+        <v>104</v>
+      </c>
+      <c r="B72" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A73" t="s">
+        <v>105</v>
+      </c>
+      <c r="B73" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A74" t="s">
+        <v>117</v>
+      </c>
+      <c r="B74" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="76" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="77" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="78" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="79" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="80" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Feuil1"/>
+  <dimension ref="A1:Z937"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" customWidth="1"/>
+    <col min="4" max="26" width="65.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+    </row>
+    <row r="2" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="17" ht="14.25" customHeight="1"/>
+    <row r="18" ht="14.25" customHeight="1"/>
+    <row r="19" ht="14.25" customHeight="1"/>
+    <row r="20" ht="14.25" customHeight="1"/>
+    <row r="21" ht="14.25" customHeight="1"/>
+    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="23" ht="14.25" customHeight="1"/>
+    <row r="24" ht="14.25" customHeight="1"/>
+    <row r="25" ht="14.25" customHeight="1"/>
+    <row r="26" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="29" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1"/>
+    <row r="32" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -3159,1599 +4461,6 @@
     <row r="935" ht="14.25" customHeight="1"/>
     <row r="936" ht="14.25" customHeight="1"/>
     <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-  </sheetData>
-  <phoneticPr fontId="2"/>
-  <hyperlinks>
-    <hyperlink ref="B27" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Feuil1"/>
-  <dimension ref="A1:Z994"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" customWidth="1"/>
-    <col min="4" max="26" width="65.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-    </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" ht="14.1" customHeight="1">
-      <c r="A15" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="14.1" customHeight="1">
-      <c r="A16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A20" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A22" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A23" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A24" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A25" t="s">
-        <v>98</v>
-      </c>
-      <c r="B25" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A26" t="s">
-        <v>99</v>
-      </c>
-      <c r="B26" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A27" t="s">
-        <v>100</v>
-      </c>
-      <c r="B27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A28" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A29" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A30" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" t="s">
-        <v>116</v>
-      </c>
-      <c r="C30" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A31" t="s">
-        <v>104</v>
-      </c>
-      <c r="B31" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A32" t="s">
-        <v>105</v>
-      </c>
-      <c r="B32" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A33" t="s">
-        <v>106</v>
-      </c>
-      <c r="B33" t="s">
-        <v>119</v>
-      </c>
-      <c r="C33" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A34" t="s">
-        <v>107</v>
-      </c>
-      <c r="B34" t="s">
-        <v>120</v>
-      </c>
-      <c r="C34" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C35" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A36" t="s">
-        <v>122</v>
-      </c>
-      <c r="B36" t="s">
-        <v>133</v>
-      </c>
-      <c r="C36" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A37" t="s">
-        <v>123</v>
-      </c>
-      <c r="B37" t="s">
-        <v>134</v>
-      </c>
-      <c r="C37" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A38" t="s">
-        <v>124</v>
-      </c>
-      <c r="B38" t="s">
-        <v>135</v>
-      </c>
-      <c r="C38" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A39" t="s">
-        <v>125</v>
-      </c>
-      <c r="B39" t="s">
-        <v>136</v>
-      </c>
-      <c r="C39" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A40" t="s">
-        <v>126</v>
-      </c>
-      <c r="B40" t="s">
-        <v>137</v>
-      </c>
-      <c r="C40" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A41" t="s">
-        <v>127</v>
-      </c>
-      <c r="B41" t="s">
-        <v>138</v>
-      </c>
-      <c r="C41" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A42" t="s">
-        <v>128</v>
-      </c>
-      <c r="B42" t="s">
-        <v>139</v>
-      </c>
-      <c r="C42" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A43" t="s">
-        <v>129</v>
-      </c>
-      <c r="B43" t="s">
-        <v>140</v>
-      </c>
-      <c r="C43" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A44" t="s">
-        <v>130</v>
-      </c>
-      <c r="B44" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A45" t="s">
-        <v>131</v>
-      </c>
-      <c r="B45" t="s">
-        <v>142</v>
-      </c>
-      <c r="C45" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A46" t="s">
-        <v>143</v>
-      </c>
-      <c r="B46" t="s">
-        <v>144</v>
-      </c>
-      <c r="C46" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="48" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="49" ht="14.25" customHeight="1"/>
-    <row r="50" ht="14.25" customHeight="1"/>
-    <row r="51" ht="14.25" customHeight="1"/>
-    <row r="52" ht="14.25" customHeight="1"/>
-    <row r="53" ht="14.25" customHeight="1"/>
-    <row r="54" ht="14.25" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1"/>
-    <row r="56" ht="14.25" customHeight="1"/>
-    <row r="57" ht="14.25" customHeight="1"/>
-    <row r="58" ht="14.25" customHeight="1"/>
-    <row r="59" ht="14.25" customHeight="1"/>
-    <row r="60" ht="14.25" customHeight="1"/>
-    <row r="61" ht="14.25" customHeight="1"/>
-    <row r="62" ht="14.25" customHeight="1"/>
-    <row r="63" ht="14.25" customHeight="1"/>
-    <row r="64" ht="14.25" customHeight="1"/>
-    <row r="65" ht="14.25" customHeight="1"/>
-    <row r="66" ht="14.25" customHeight="1"/>
-    <row r="67" ht="14.25" customHeight="1"/>
-    <row r="68" ht="14.25" customHeight="1"/>
-    <row r="69" ht="14.25" customHeight="1"/>
-    <row r="70" ht="14.25" customHeight="1"/>
-    <row r="71" ht="14.25" customHeight="1"/>
-    <row r="72" ht="14.25" customHeight="1"/>
-    <row r="73" ht="14.25" customHeight="1"/>
-    <row r="74" ht="14.25" customHeight="1"/>
-    <row r="75" ht="14.25" customHeight="1"/>
-    <row r="76" ht="14.25" customHeight="1"/>
-    <row r="77" ht="14.25" customHeight="1"/>
-    <row r="78" ht="14.25" customHeight="1"/>
-    <row r="79" ht="14.25" customHeight="1"/>
-    <row r="80" ht="14.25" customHeight="1"/>
-    <row r="81" ht="14.25" customHeight="1"/>
-    <row r="82" ht="14.25" customHeight="1"/>
-    <row r="83" ht="14.25" customHeight="1"/>
-    <row r="84" ht="14.25" customHeight="1"/>
-    <row r="85" ht="14.25" customHeight="1"/>
-    <row r="86" ht="14.25" customHeight="1"/>
-    <row r="87" ht="14.25" customHeight="1"/>
-    <row r="88" ht="14.25" customHeight="1"/>
-    <row r="89" ht="14.25" customHeight="1"/>
-    <row r="90" ht="14.25" customHeight="1"/>
-    <row r="91" ht="14.25" customHeight="1"/>
-    <row r="92" ht="14.25" customHeight="1"/>
-    <row r="93" ht="14.25" customHeight="1"/>
-    <row r="94" ht="14.25" customHeight="1"/>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
-    <row r="97" ht="14.25" customHeight="1"/>
-    <row r="98" ht="14.25" customHeight="1"/>
-    <row r="99" ht="14.25" customHeight="1"/>
-    <row r="100" ht="14.25" customHeight="1"/>
-    <row r="101" ht="14.25" customHeight="1"/>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
-    <row r="112" ht="14.25" customHeight="1"/>
-    <row r="113" ht="14.25" customHeight="1"/>
-    <row r="114" ht="14.25" customHeight="1"/>
-    <row r="115" ht="14.25" customHeight="1"/>
-    <row r="116" ht="14.25" customHeight="1"/>
-    <row r="117" ht="14.25" customHeight="1"/>
-    <row r="118" ht="14.25" customHeight="1"/>
-    <row r="119" ht="14.25" customHeight="1"/>
-    <row r="120" ht="14.25" customHeight="1"/>
-    <row r="121" ht="14.25" customHeight="1"/>
-    <row r="122" ht="14.25" customHeight="1"/>
-    <row r="123" ht="14.25" customHeight="1"/>
-    <row r="124" ht="14.25" customHeight="1"/>
-    <row r="125" ht="14.25" customHeight="1"/>
-    <row r="126" ht="14.25" customHeight="1"/>
-    <row r="127" ht="14.25" customHeight="1"/>
-    <row r="128" ht="14.25" customHeight="1"/>
-    <row r="129" ht="14.25" customHeight="1"/>
-    <row r="130" ht="14.25" customHeight="1"/>
-    <row r="131" ht="14.25" customHeight="1"/>
-    <row r="132" ht="14.25" customHeight="1"/>
-    <row r="133" ht="14.25" customHeight="1"/>
-    <row r="134" ht="14.25" customHeight="1"/>
-    <row r="135" ht="14.25" customHeight="1"/>
-    <row r="136" ht="14.25" customHeight="1"/>
-    <row r="137" ht="14.25" customHeight="1"/>
-    <row r="138" ht="14.25" customHeight="1"/>
-    <row r="139" ht="14.25" customHeight="1"/>
-    <row r="140" ht="14.25" customHeight="1"/>
-    <row r="141" ht="14.25" customHeight="1"/>
-    <row r="142" ht="14.25" customHeight="1"/>
-    <row r="143" ht="14.25" customHeight="1"/>
-    <row r="144" ht="14.25" customHeight="1"/>
-    <row r="145" ht="14.25" customHeight="1"/>
-    <row r="146" ht="14.25" customHeight="1"/>
-    <row r="147" ht="14.25" customHeight="1"/>
-    <row r="148" ht="14.25" customHeight="1"/>
-    <row r="149" ht="14.25" customHeight="1"/>
-    <row r="150" ht="14.25" customHeight="1"/>
-    <row r="151" ht="14.25" customHeight="1"/>
-    <row r="152" ht="14.25" customHeight="1"/>
-    <row r="153" ht="14.25" customHeight="1"/>
-    <row r="154" ht="14.25" customHeight="1"/>
-    <row r="155" ht="14.25" customHeight="1"/>
-    <row r="156" ht="14.25" customHeight="1"/>
-    <row r="157" ht="14.25" customHeight="1"/>
-    <row r="158" ht="14.25" customHeight="1"/>
-    <row r="159" ht="14.25" customHeight="1"/>
-    <row r="160" ht="14.25" customHeight="1"/>
-    <row r="161" ht="14.25" customHeight="1"/>
-    <row r="162" ht="14.25" customHeight="1"/>
-    <row r="163" ht="14.25" customHeight="1"/>
-    <row r="164" ht="14.25" customHeight="1"/>
-    <row r="165" ht="14.25" customHeight="1"/>
-    <row r="166" ht="14.25" customHeight="1"/>
-    <row r="167" ht="14.25" customHeight="1"/>
-    <row r="168" ht="14.25" customHeight="1"/>
-    <row r="169" ht="14.25" customHeight="1"/>
-    <row r="170" ht="14.25" customHeight="1"/>
-    <row r="171" ht="14.25" customHeight="1"/>
-    <row r="172" ht="14.25" customHeight="1"/>
-    <row r="173" ht="14.25" customHeight="1"/>
-    <row r="174" ht="14.25" customHeight="1"/>
-    <row r="175" ht="14.25" customHeight="1"/>
-    <row r="176" ht="14.25" customHeight="1"/>
-    <row r="177" ht="14.25" customHeight="1"/>
-    <row r="178" ht="14.25" customHeight="1"/>
-    <row r="179" ht="14.25" customHeight="1"/>
-    <row r="180" ht="14.25" customHeight="1"/>
-    <row r="181" ht="14.25" customHeight="1"/>
-    <row r="182" ht="14.25" customHeight="1"/>
-    <row r="183" ht="14.25" customHeight="1"/>
-    <row r="184" ht="14.25" customHeight="1"/>
-    <row r="185" ht="14.25" customHeight="1"/>
-    <row r="186" ht="14.25" customHeight="1"/>
-    <row r="187" ht="14.25" customHeight="1"/>
-    <row r="188" ht="14.25" customHeight="1"/>
-    <row r="189" ht="14.25" customHeight="1"/>
-    <row r="190" ht="14.25" customHeight="1"/>
-    <row r="191" ht="14.25" customHeight="1"/>
-    <row r="192" ht="14.25" customHeight="1"/>
-    <row r="193" ht="14.25" customHeight="1"/>
-    <row r="194" ht="14.25" customHeight="1"/>
-    <row r="195" ht="14.25" customHeight="1"/>
-    <row r="196" ht="14.25" customHeight="1"/>
-    <row r="197" ht="14.25" customHeight="1"/>
-    <row r="198" ht="14.25" customHeight="1"/>
-    <row r="199" ht="14.25" customHeight="1"/>
-    <row r="200" ht="14.25" customHeight="1"/>
-    <row r="201" ht="14.25" customHeight="1"/>
-    <row r="202" ht="14.25" customHeight="1"/>
-    <row r="203" ht="14.25" customHeight="1"/>
-    <row r="204" ht="14.25" customHeight="1"/>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
-    <row r="209" ht="14.25" customHeight="1"/>
-    <row r="210" ht="14.25" customHeight="1"/>
-    <row r="211" ht="14.25" customHeight="1"/>
-    <row r="212" ht="14.25" customHeight="1"/>
-    <row r="213" ht="14.25" customHeight="1"/>
-    <row r="214" ht="14.25" customHeight="1"/>
-    <row r="215" ht="14.25" customHeight="1"/>
-    <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
-    <row r="219" ht="14.25" customHeight="1"/>
-    <row r="220" ht="14.25" customHeight="1"/>
-    <row r="221" ht="14.25" customHeight="1"/>
-    <row r="222" ht="14.25" customHeight="1"/>
-    <row r="223" ht="14.25" customHeight="1"/>
-    <row r="224" ht="14.25" customHeight="1"/>
-    <row r="225" ht="14.25" customHeight="1"/>
-    <row r="226" ht="14.25" customHeight="1"/>
-    <row r="227" ht="14.25" customHeight="1"/>
-    <row r="228" ht="14.25" customHeight="1"/>
-    <row r="229" ht="14.25" customHeight="1"/>
-    <row r="230" ht="14.25" customHeight="1"/>
-    <row r="231" ht="14.25" customHeight="1"/>
-    <row r="232" ht="14.25" customHeight="1"/>
-    <row r="233" ht="14.25" customHeight="1"/>
-    <row r="234" ht="14.25" customHeight="1"/>
-    <row r="235" ht="14.25" customHeight="1"/>
-    <row r="236" ht="14.25" customHeight="1"/>
-    <row r="237" ht="14.25" customHeight="1"/>
-    <row r="238" ht="14.25" customHeight="1"/>
-    <row r="239" ht="14.25" customHeight="1"/>
-    <row r="240" ht="14.25" customHeight="1"/>
-    <row r="241" ht="14.25" customHeight="1"/>
-    <row r="242" ht="14.25" customHeight="1"/>
-    <row r="243" ht="14.25" customHeight="1"/>
-    <row r="244" ht="14.25" customHeight="1"/>
-    <row r="245" ht="14.25" customHeight="1"/>
-    <row r="246" ht="14.25" customHeight="1"/>
-    <row r="247" ht="14.25" customHeight="1"/>
-    <row r="248" ht="14.25" customHeight="1"/>
-    <row r="249" ht="14.25" customHeight="1"/>
-    <row r="250" ht="14.25" customHeight="1"/>
-    <row r="251" ht="14.25" customHeight="1"/>
-    <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="14.25" customHeight="1"/>
-    <row r="254" ht="14.25" customHeight="1"/>
-    <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="14.25" customHeight="1"/>
-    <row r="257" ht="14.25" customHeight="1"/>
-    <row r="258" ht="14.25" customHeight="1"/>
-    <row r="259" ht="14.25" customHeight="1"/>
-    <row r="260" ht="14.25" customHeight="1"/>
-    <row r="261" ht="14.25" customHeight="1"/>
-    <row r="262" ht="14.25" customHeight="1"/>
-    <row r="263" ht="14.25" customHeight="1"/>
-    <row r="264" ht="14.25" customHeight="1"/>
-    <row r="265" ht="14.25" customHeight="1"/>
-    <row r="266" ht="14.25" customHeight="1"/>
-    <row r="267" ht="14.25" customHeight="1"/>
-    <row r="268" ht="14.25" customHeight="1"/>
-    <row r="269" ht="14.25" customHeight="1"/>
-    <row r="270" ht="14.25" customHeight="1"/>
-    <row r="271" ht="14.25" customHeight="1"/>
-    <row r="272" ht="14.25" customHeight="1"/>
-    <row r="273" ht="14.25" customHeight="1"/>
-    <row r="274" ht="14.25" customHeight="1"/>
-    <row r="275" ht="14.25" customHeight="1"/>
-    <row r="276" ht="14.25" customHeight="1"/>
-    <row r="277" ht="14.25" customHeight="1"/>
-    <row r="278" ht="14.25" customHeight="1"/>
-    <row r="279" ht="14.25" customHeight="1"/>
-    <row r="280" ht="14.25" customHeight="1"/>
-    <row r="281" ht="14.25" customHeight="1"/>
-    <row r="282" ht="14.25" customHeight="1"/>
-    <row r="283" ht="14.25" customHeight="1"/>
-    <row r="284" ht="14.25" customHeight="1"/>
-    <row r="285" ht="14.25" customHeight="1"/>
-    <row r="286" ht="14.25" customHeight="1"/>
-    <row r="287" ht="14.25" customHeight="1"/>
-    <row r="288" ht="14.25" customHeight="1"/>
-    <row r="289" ht="14.25" customHeight="1"/>
-    <row r="290" ht="14.25" customHeight="1"/>
-    <row r="291" ht="14.25" customHeight="1"/>
-    <row r="292" ht="14.25" customHeight="1"/>
-    <row r="293" ht="14.25" customHeight="1"/>
-    <row r="294" ht="14.25" customHeight="1"/>
-    <row r="295" ht="14.25" customHeight="1"/>
-    <row r="296" ht="14.25" customHeight="1"/>
-    <row r="297" ht="14.25" customHeight="1"/>
-    <row r="298" ht="14.25" customHeight="1"/>
-    <row r="299" ht="14.25" customHeight="1"/>
-    <row r="300" ht="14.25" customHeight="1"/>
-    <row r="301" ht="14.25" customHeight="1"/>
-    <row r="302" ht="14.25" customHeight="1"/>
-    <row r="303" ht="14.25" customHeight="1"/>
-    <row r="304" ht="14.25" customHeight="1"/>
-    <row r="305" ht="14.25" customHeight="1"/>
-    <row r="306" ht="14.25" customHeight="1"/>
-    <row r="307" ht="14.25" customHeight="1"/>
-    <row r="308" ht="14.25" customHeight="1"/>
-    <row r="309" ht="14.25" customHeight="1"/>
-    <row r="310" ht="14.25" customHeight="1"/>
-    <row r="311" ht="14.25" customHeight="1"/>
-    <row r="312" ht="14.25" customHeight="1"/>
-    <row r="313" ht="14.25" customHeight="1"/>
-    <row r="314" ht="14.25" customHeight="1"/>
-    <row r="315" ht="14.25" customHeight="1"/>
-    <row r="316" ht="14.25" customHeight="1"/>
-    <row r="317" ht="14.25" customHeight="1"/>
-    <row r="318" ht="14.25" customHeight="1"/>
-    <row r="319" ht="14.25" customHeight="1"/>
-    <row r="320" ht="14.25" customHeight="1"/>
-    <row r="321" ht="14.25" customHeight="1"/>
-    <row r="322" ht="14.25" customHeight="1"/>
-    <row r="323" ht="14.25" customHeight="1"/>
-    <row r="324" ht="14.25" customHeight="1"/>
-    <row r="325" ht="14.25" customHeight="1"/>
-    <row r="326" ht="14.25" customHeight="1"/>
-    <row r="327" ht="14.25" customHeight="1"/>
-    <row r="328" ht="14.25" customHeight="1"/>
-    <row r="329" ht="14.25" customHeight="1"/>
-    <row r="330" ht="14.25" customHeight="1"/>
-    <row r="331" ht="14.25" customHeight="1"/>
-    <row r="332" ht="14.25" customHeight="1"/>
-    <row r="333" ht="14.25" customHeight="1"/>
-    <row r="334" ht="14.25" customHeight="1"/>
-    <row r="335" ht="14.25" customHeight="1"/>
-    <row r="336" ht="14.25" customHeight="1"/>
-    <row r="337" ht="14.25" customHeight="1"/>
-    <row r="338" ht="14.25" customHeight="1"/>
-    <row r="339" ht="14.25" customHeight="1"/>
-    <row r="340" ht="14.25" customHeight="1"/>
-    <row r="341" ht="14.25" customHeight="1"/>
-    <row r="342" ht="14.25" customHeight="1"/>
-    <row r="343" ht="14.25" customHeight="1"/>
-    <row r="344" ht="14.25" customHeight="1"/>
-    <row r="345" ht="14.25" customHeight="1"/>
-    <row r="346" ht="14.25" customHeight="1"/>
-    <row r="347" ht="14.25" customHeight="1"/>
-    <row r="348" ht="14.25" customHeight="1"/>
-    <row r="349" ht="14.25" customHeight="1"/>
-    <row r="350" ht="14.25" customHeight="1"/>
-    <row r="351" ht="14.25" customHeight="1"/>
-    <row r="352" ht="14.25" customHeight="1"/>
-    <row r="353" ht="14.25" customHeight="1"/>
-    <row r="354" ht="14.25" customHeight="1"/>
-    <row r="355" ht="14.25" customHeight="1"/>
-    <row r="356" ht="14.25" customHeight="1"/>
-    <row r="357" ht="14.25" customHeight="1"/>
-    <row r="358" ht="14.25" customHeight="1"/>
-    <row r="359" ht="14.25" customHeight="1"/>
-    <row r="360" ht="14.25" customHeight="1"/>
-    <row r="361" ht="14.25" customHeight="1"/>
-    <row r="362" ht="14.25" customHeight="1"/>
-    <row r="363" ht="14.25" customHeight="1"/>
-    <row r="364" ht="14.25" customHeight="1"/>
-    <row r="365" ht="14.25" customHeight="1"/>
-    <row r="366" ht="14.25" customHeight="1"/>
-    <row r="367" ht="14.25" customHeight="1"/>
-    <row r="368" ht="14.25" customHeight="1"/>
-    <row r="369" ht="14.25" customHeight="1"/>
-    <row r="370" ht="14.25" customHeight="1"/>
-    <row r="371" ht="14.25" customHeight="1"/>
-    <row r="372" ht="14.25" customHeight="1"/>
-    <row r="373" ht="14.25" customHeight="1"/>
-    <row r="374" ht="14.25" customHeight="1"/>
-    <row r="375" ht="14.25" customHeight="1"/>
-    <row r="376" ht="14.25" customHeight="1"/>
-    <row r="377" ht="14.25" customHeight="1"/>
-    <row r="378" ht="14.25" customHeight="1"/>
-    <row r="379" ht="14.25" customHeight="1"/>
-    <row r="380" ht="14.25" customHeight="1"/>
-    <row r="381" ht="14.25" customHeight="1"/>
-    <row r="382" ht="14.25" customHeight="1"/>
-    <row r="383" ht="14.25" customHeight="1"/>
-    <row r="384" ht="14.25" customHeight="1"/>
-    <row r="385" ht="14.25" customHeight="1"/>
-    <row r="386" ht="14.25" customHeight="1"/>
-    <row r="387" ht="14.25" customHeight="1"/>
-    <row r="388" ht="14.25" customHeight="1"/>
-    <row r="389" ht="14.25" customHeight="1"/>
-    <row r="390" ht="14.25" customHeight="1"/>
-    <row r="391" ht="14.25" customHeight="1"/>
-    <row r="392" ht="14.25" customHeight="1"/>
-    <row r="393" ht="14.25" customHeight="1"/>
-    <row r="394" ht="14.25" customHeight="1"/>
-    <row r="395" ht="14.25" customHeight="1"/>
-    <row r="396" ht="14.25" customHeight="1"/>
-    <row r="397" ht="14.25" customHeight="1"/>
-    <row r="398" ht="14.25" customHeight="1"/>
-    <row r="399" ht="14.25" customHeight="1"/>
-    <row r="400" ht="14.25" customHeight="1"/>
-    <row r="401" ht="14.25" customHeight="1"/>
-    <row r="402" ht="14.25" customHeight="1"/>
-    <row r="403" ht="14.25" customHeight="1"/>
-    <row r="404" ht="14.25" customHeight="1"/>
-    <row r="405" ht="14.25" customHeight="1"/>
-    <row r="406" ht="14.25" customHeight="1"/>
-    <row r="407" ht="14.25" customHeight="1"/>
-    <row r="408" ht="14.25" customHeight="1"/>
-    <row r="409" ht="14.25" customHeight="1"/>
-    <row r="410" ht="14.25" customHeight="1"/>
-    <row r="411" ht="14.25" customHeight="1"/>
-    <row r="412" ht="14.25" customHeight="1"/>
-    <row r="413" ht="14.25" customHeight="1"/>
-    <row r="414" ht="14.25" customHeight="1"/>
-    <row r="415" ht="14.25" customHeight="1"/>
-    <row r="416" ht="14.25" customHeight="1"/>
-    <row r="417" ht="14.25" customHeight="1"/>
-    <row r="418" ht="14.25" customHeight="1"/>
-    <row r="419" ht="14.25" customHeight="1"/>
-    <row r="420" ht="14.25" customHeight="1"/>
-    <row r="421" ht="14.25" customHeight="1"/>
-    <row r="422" ht="14.25" customHeight="1"/>
-    <row r="423" ht="14.25" customHeight="1"/>
-    <row r="424" ht="14.25" customHeight="1"/>
-    <row r="425" ht="14.25" customHeight="1"/>
-    <row r="426" ht="14.25" customHeight="1"/>
-    <row r="427" ht="14.25" customHeight="1"/>
-    <row r="428" ht="14.25" customHeight="1"/>
-    <row r="429" ht="14.25" customHeight="1"/>
-    <row r="430" ht="14.25" customHeight="1"/>
-    <row r="431" ht="14.25" customHeight="1"/>
-    <row r="432" ht="14.25" customHeight="1"/>
-    <row r="433" ht="14.25" customHeight="1"/>
-    <row r="434" ht="14.25" customHeight="1"/>
-    <row r="435" ht="14.25" customHeight="1"/>
-    <row r="436" ht="14.25" customHeight="1"/>
-    <row r="437" ht="14.25" customHeight="1"/>
-    <row r="438" ht="14.25" customHeight="1"/>
-    <row r="439" ht="14.25" customHeight="1"/>
-    <row r="440" ht="14.25" customHeight="1"/>
-    <row r="441" ht="14.25" customHeight="1"/>
-    <row r="442" ht="14.25" customHeight="1"/>
-    <row r="443" ht="14.25" customHeight="1"/>
-    <row r="444" ht="14.25" customHeight="1"/>
-    <row r="445" ht="14.25" customHeight="1"/>
-    <row r="446" ht="14.25" customHeight="1"/>
-    <row r="447" ht="14.25" customHeight="1"/>
-    <row r="448" ht="14.25" customHeight="1"/>
-    <row r="449" ht="14.25" customHeight="1"/>
-    <row r="450" ht="14.25" customHeight="1"/>
-    <row r="451" ht="14.25" customHeight="1"/>
-    <row r="452" ht="14.25" customHeight="1"/>
-    <row r="453" ht="14.25" customHeight="1"/>
-    <row r="454" ht="14.25" customHeight="1"/>
-    <row r="455" ht="14.25" customHeight="1"/>
-    <row r="456" ht="14.25" customHeight="1"/>
-    <row r="457" ht="14.25" customHeight="1"/>
-    <row r="458" ht="14.25" customHeight="1"/>
-    <row r="459" ht="14.25" customHeight="1"/>
-    <row r="460" ht="14.25" customHeight="1"/>
-    <row r="461" ht="14.25" customHeight="1"/>
-    <row r="462" ht="14.25" customHeight="1"/>
-    <row r="463" ht="14.25" customHeight="1"/>
-    <row r="464" ht="14.25" customHeight="1"/>
-    <row r="465" ht="14.25" customHeight="1"/>
-    <row r="466" ht="14.25" customHeight="1"/>
-    <row r="467" ht="14.25" customHeight="1"/>
-    <row r="468" ht="14.25" customHeight="1"/>
-    <row r="469" ht="14.25" customHeight="1"/>
-    <row r="470" ht="14.25" customHeight="1"/>
-    <row r="471" ht="14.25" customHeight="1"/>
-    <row r="472" ht="14.25" customHeight="1"/>
-    <row r="473" ht="14.25" customHeight="1"/>
-    <row r="474" ht="14.25" customHeight="1"/>
-    <row r="475" ht="14.25" customHeight="1"/>
-    <row r="476" ht="14.25" customHeight="1"/>
-    <row r="477" ht="14.25" customHeight="1"/>
-    <row r="478" ht="14.25" customHeight="1"/>
-    <row r="479" ht="14.25" customHeight="1"/>
-    <row r="480" ht="14.25" customHeight="1"/>
-    <row r="481" ht="14.25" customHeight="1"/>
-    <row r="482" ht="14.25" customHeight="1"/>
-    <row r="483" ht="14.25" customHeight="1"/>
-    <row r="484" ht="14.25" customHeight="1"/>
-    <row r="485" ht="14.25" customHeight="1"/>
-    <row r="486" ht="14.25" customHeight="1"/>
-    <row r="487" ht="14.25" customHeight="1"/>
-    <row r="488" ht="14.25" customHeight="1"/>
-    <row r="489" ht="14.25" customHeight="1"/>
-    <row r="490" ht="14.25" customHeight="1"/>
-    <row r="491" ht="14.25" customHeight="1"/>
-    <row r="492" ht="14.25" customHeight="1"/>
-    <row r="493" ht="14.25" customHeight="1"/>
-    <row r="494" ht="14.25" customHeight="1"/>
-    <row r="495" ht="14.25" customHeight="1"/>
-    <row r="496" ht="14.25" customHeight="1"/>
-    <row r="497" ht="14.25" customHeight="1"/>
-    <row r="498" ht="14.25" customHeight="1"/>
-    <row r="499" ht="14.25" customHeight="1"/>
-    <row r="500" ht="14.25" customHeight="1"/>
-    <row r="501" ht="14.25" customHeight="1"/>
-    <row r="502" ht="14.25" customHeight="1"/>
-    <row r="503" ht="14.25" customHeight="1"/>
-    <row r="504" ht="14.25" customHeight="1"/>
-    <row r="505" ht="14.25" customHeight="1"/>
-    <row r="506" ht="14.25" customHeight="1"/>
-    <row r="507" ht="14.25" customHeight="1"/>
-    <row r="508" ht="14.25" customHeight="1"/>
-    <row r="509" ht="14.25" customHeight="1"/>
-    <row r="510" ht="14.25" customHeight="1"/>
-    <row r="511" ht="14.25" customHeight="1"/>
-    <row r="512" ht="14.25" customHeight="1"/>
-    <row r="513" ht="14.25" customHeight="1"/>
-    <row r="514" ht="14.25" customHeight="1"/>
-    <row r="515" ht="14.25" customHeight="1"/>
-    <row r="516" ht="14.25" customHeight="1"/>
-    <row r="517" ht="14.25" customHeight="1"/>
-    <row r="518" ht="14.25" customHeight="1"/>
-    <row r="519" ht="14.25" customHeight="1"/>
-    <row r="520" ht="14.25" customHeight="1"/>
-    <row r="521" ht="14.25" customHeight="1"/>
-    <row r="522" ht="14.25" customHeight="1"/>
-    <row r="523" ht="14.25" customHeight="1"/>
-    <row r="524" ht="14.25" customHeight="1"/>
-    <row r="525" ht="14.25" customHeight="1"/>
-    <row r="526" ht="14.25" customHeight="1"/>
-    <row r="527" ht="14.25" customHeight="1"/>
-    <row r="528" ht="14.25" customHeight="1"/>
-    <row r="529" ht="14.25" customHeight="1"/>
-    <row r="530" ht="14.25" customHeight="1"/>
-    <row r="531" ht="14.25" customHeight="1"/>
-    <row r="532" ht="14.25" customHeight="1"/>
-    <row r="533" ht="14.25" customHeight="1"/>
-    <row r="534" ht="14.25" customHeight="1"/>
-    <row r="535" ht="14.25" customHeight="1"/>
-    <row r="536" ht="14.25" customHeight="1"/>
-    <row r="537" ht="14.25" customHeight="1"/>
-    <row r="538" ht="14.25" customHeight="1"/>
-    <row r="539" ht="14.25" customHeight="1"/>
-    <row r="540" ht="14.25" customHeight="1"/>
-    <row r="541" ht="14.25" customHeight="1"/>
-    <row r="542" ht="14.25" customHeight="1"/>
-    <row r="543" ht="14.25" customHeight="1"/>
-    <row r="544" ht="14.25" customHeight="1"/>
-    <row r="545" ht="14.25" customHeight="1"/>
-    <row r="546" ht="14.25" customHeight="1"/>
-    <row r="547" ht="14.25" customHeight="1"/>
-    <row r="548" ht="14.25" customHeight="1"/>
-    <row r="549" ht="14.25" customHeight="1"/>
-    <row r="550" ht="14.25" customHeight="1"/>
-    <row r="551" ht="14.25" customHeight="1"/>
-    <row r="552" ht="14.25" customHeight="1"/>
-    <row r="553" ht="14.25" customHeight="1"/>
-    <row r="554" ht="14.25" customHeight="1"/>
-    <row r="555" ht="14.25" customHeight="1"/>
-    <row r="556" ht="14.25" customHeight="1"/>
-    <row r="557" ht="14.25" customHeight="1"/>
-    <row r="558" ht="14.25" customHeight="1"/>
-    <row r="559" ht="14.25" customHeight="1"/>
-    <row r="560" ht="14.25" customHeight="1"/>
-    <row r="561" ht="14.25" customHeight="1"/>
-    <row r="562" ht="14.25" customHeight="1"/>
-    <row r="563" ht="14.25" customHeight="1"/>
-    <row r="564" ht="14.25" customHeight="1"/>
-    <row r="565" ht="14.25" customHeight="1"/>
-    <row r="566" ht="14.25" customHeight="1"/>
-    <row r="567" ht="14.25" customHeight="1"/>
-    <row r="568" ht="14.25" customHeight="1"/>
-    <row r="569" ht="14.25" customHeight="1"/>
-    <row r="570" ht="14.25" customHeight="1"/>
-    <row r="571" ht="14.25" customHeight="1"/>
-    <row r="572" ht="14.25" customHeight="1"/>
-    <row r="573" ht="14.25" customHeight="1"/>
-    <row r="574" ht="14.25" customHeight="1"/>
-    <row r="575" ht="14.25" customHeight="1"/>
-    <row r="576" ht="14.25" customHeight="1"/>
-    <row r="577" ht="14.25" customHeight="1"/>
-    <row r="578" ht="14.25" customHeight="1"/>
-    <row r="579" ht="14.25" customHeight="1"/>
-    <row r="580" ht="14.25" customHeight="1"/>
-    <row r="581" ht="14.25" customHeight="1"/>
-    <row r="582" ht="14.25" customHeight="1"/>
-    <row r="583" ht="14.25" customHeight="1"/>
-    <row r="584" ht="14.25" customHeight="1"/>
-    <row r="585" ht="14.25" customHeight="1"/>
-    <row r="586" ht="14.25" customHeight="1"/>
-    <row r="587" ht="14.25" customHeight="1"/>
-    <row r="588" ht="14.25" customHeight="1"/>
-    <row r="589" ht="14.25" customHeight="1"/>
-    <row r="590" ht="14.25" customHeight="1"/>
-    <row r="591" ht="14.25" customHeight="1"/>
-    <row r="592" ht="14.25" customHeight="1"/>
-    <row r="593" ht="14.25" customHeight="1"/>
-    <row r="594" ht="14.25" customHeight="1"/>
-    <row r="595" ht="14.25" customHeight="1"/>
-    <row r="596" ht="14.25" customHeight="1"/>
-    <row r="597" ht="14.25" customHeight="1"/>
-    <row r="598" ht="14.25" customHeight="1"/>
-    <row r="599" ht="14.25" customHeight="1"/>
-    <row r="600" ht="14.25" customHeight="1"/>
-    <row r="601" ht="14.25" customHeight="1"/>
-    <row r="602" ht="14.25" customHeight="1"/>
-    <row r="603" ht="14.25" customHeight="1"/>
-    <row r="604" ht="14.25" customHeight="1"/>
-    <row r="605" ht="14.25" customHeight="1"/>
-    <row r="606" ht="14.25" customHeight="1"/>
-    <row r="607" ht="14.25" customHeight="1"/>
-    <row r="608" ht="14.25" customHeight="1"/>
-    <row r="609" ht="14.25" customHeight="1"/>
-    <row r="610" ht="14.25" customHeight="1"/>
-    <row r="611" ht="14.25" customHeight="1"/>
-    <row r="612" ht="14.25" customHeight="1"/>
-    <row r="613" ht="14.25" customHeight="1"/>
-    <row r="614" ht="14.25" customHeight="1"/>
-    <row r="615" ht="14.25" customHeight="1"/>
-    <row r="616" ht="14.25" customHeight="1"/>
-    <row r="617" ht="14.25" customHeight="1"/>
-    <row r="618" ht="14.25" customHeight="1"/>
-    <row r="619" ht="14.25" customHeight="1"/>
-    <row r="620" ht="14.25" customHeight="1"/>
-    <row r="621" ht="14.25" customHeight="1"/>
-    <row r="622" ht="14.25" customHeight="1"/>
-    <row r="623" ht="14.25" customHeight="1"/>
-    <row r="624" ht="14.25" customHeight="1"/>
-    <row r="625" ht="14.25" customHeight="1"/>
-    <row r="626" ht="14.25" customHeight="1"/>
-    <row r="627" ht="14.25" customHeight="1"/>
-    <row r="628" ht="14.25" customHeight="1"/>
-    <row r="629" ht="14.25" customHeight="1"/>
-    <row r="630" ht="14.25" customHeight="1"/>
-    <row r="631" ht="14.25" customHeight="1"/>
-    <row r="632" ht="14.25" customHeight="1"/>
-    <row r="633" ht="14.25" customHeight="1"/>
-    <row r="634" ht="14.25" customHeight="1"/>
-    <row r="635" ht="14.25" customHeight="1"/>
-    <row r="636" ht="14.25" customHeight="1"/>
-    <row r="637" ht="14.25" customHeight="1"/>
-    <row r="638" ht="14.25" customHeight="1"/>
-    <row r="639" ht="14.25" customHeight="1"/>
-    <row r="640" ht="14.25" customHeight="1"/>
-    <row r="641" ht="14.25" customHeight="1"/>
-    <row r="642" ht="14.25" customHeight="1"/>
-    <row r="643" ht="14.25" customHeight="1"/>
-    <row r="644" ht="14.25" customHeight="1"/>
-    <row r="645" ht="14.25" customHeight="1"/>
-    <row r="646" ht="14.25" customHeight="1"/>
-    <row r="647" ht="14.25" customHeight="1"/>
-    <row r="648" ht="14.25" customHeight="1"/>
-    <row r="649" ht="14.25" customHeight="1"/>
-    <row r="650" ht="14.25" customHeight="1"/>
-    <row r="651" ht="14.25" customHeight="1"/>
-    <row r="652" ht="14.25" customHeight="1"/>
-    <row r="653" ht="14.25" customHeight="1"/>
-    <row r="654" ht="14.25" customHeight="1"/>
-    <row r="655" ht="14.25" customHeight="1"/>
-    <row r="656" ht="14.25" customHeight="1"/>
-    <row r="657" ht="14.25" customHeight="1"/>
-    <row r="658" ht="14.25" customHeight="1"/>
-    <row r="659" ht="14.25" customHeight="1"/>
-    <row r="660" ht="14.25" customHeight="1"/>
-    <row r="661" ht="14.25" customHeight="1"/>
-    <row r="662" ht="14.25" customHeight="1"/>
-    <row r="663" ht="14.25" customHeight="1"/>
-    <row r="664" ht="14.25" customHeight="1"/>
-    <row r="665" ht="14.25" customHeight="1"/>
-    <row r="666" ht="14.25" customHeight="1"/>
-    <row r="667" ht="14.25" customHeight="1"/>
-    <row r="668" ht="14.25" customHeight="1"/>
-    <row r="669" ht="14.25" customHeight="1"/>
-    <row r="670" ht="14.25" customHeight="1"/>
-    <row r="671" ht="14.25" customHeight="1"/>
-    <row r="672" ht="14.25" customHeight="1"/>
-    <row r="673" ht="14.25" customHeight="1"/>
-    <row r="674" ht="14.25" customHeight="1"/>
-    <row r="675" ht="14.25" customHeight="1"/>
-    <row r="676" ht="14.25" customHeight="1"/>
-    <row r="677" ht="14.25" customHeight="1"/>
-    <row r="678" ht="14.25" customHeight="1"/>
-    <row r="679" ht="14.25" customHeight="1"/>
-    <row r="680" ht="14.25" customHeight="1"/>
-    <row r="681" ht="14.25" customHeight="1"/>
-    <row r="682" ht="14.25" customHeight="1"/>
-    <row r="683" ht="14.25" customHeight="1"/>
-    <row r="684" ht="14.25" customHeight="1"/>
-    <row r="685" ht="14.25" customHeight="1"/>
-    <row r="686" ht="14.25" customHeight="1"/>
-    <row r="687" ht="14.25" customHeight="1"/>
-    <row r="688" ht="14.25" customHeight="1"/>
-    <row r="689" ht="14.25" customHeight="1"/>
-    <row r="690" ht="14.25" customHeight="1"/>
-    <row r="691" ht="14.25" customHeight="1"/>
-    <row r="692" ht="14.25" customHeight="1"/>
-    <row r="693" ht="14.25" customHeight="1"/>
-    <row r="694" ht="14.25" customHeight="1"/>
-    <row r="695" ht="14.25" customHeight="1"/>
-    <row r="696" ht="14.25" customHeight="1"/>
-    <row r="697" ht="14.25" customHeight="1"/>
-    <row r="698" ht="14.25" customHeight="1"/>
-    <row r="699" ht="14.25" customHeight="1"/>
-    <row r="700" ht="14.25" customHeight="1"/>
-    <row r="701" ht="14.25" customHeight="1"/>
-    <row r="702" ht="14.25" customHeight="1"/>
-    <row r="703" ht="14.25" customHeight="1"/>
-    <row r="704" ht="14.25" customHeight="1"/>
-    <row r="705" ht="14.25" customHeight="1"/>
-    <row r="706" ht="14.25" customHeight="1"/>
-    <row r="707" ht="14.25" customHeight="1"/>
-    <row r="708" ht="14.25" customHeight="1"/>
-    <row r="709" ht="14.25" customHeight="1"/>
-    <row r="710" ht="14.25" customHeight="1"/>
-    <row r="711" ht="14.25" customHeight="1"/>
-    <row r="712" ht="14.25" customHeight="1"/>
-    <row r="713" ht="14.25" customHeight="1"/>
-    <row r="714" ht="14.25" customHeight="1"/>
-    <row r="715" ht="14.25" customHeight="1"/>
-    <row r="716" ht="14.25" customHeight="1"/>
-    <row r="717" ht="14.25" customHeight="1"/>
-    <row r="718" ht="14.25" customHeight="1"/>
-    <row r="719" ht="14.25" customHeight="1"/>
-    <row r="720" ht="14.25" customHeight="1"/>
-    <row r="721" ht="14.25" customHeight="1"/>
-    <row r="722" ht="14.25" customHeight="1"/>
-    <row r="723" ht="14.25" customHeight="1"/>
-    <row r="724" ht="14.25" customHeight="1"/>
-    <row r="725" ht="14.25" customHeight="1"/>
-    <row r="726" ht="14.25" customHeight="1"/>
-    <row r="727" ht="14.25" customHeight="1"/>
-    <row r="728" ht="14.25" customHeight="1"/>
-    <row r="729" ht="14.25" customHeight="1"/>
-    <row r="730" ht="14.25" customHeight="1"/>
-    <row r="731" ht="14.25" customHeight="1"/>
-    <row r="732" ht="14.25" customHeight="1"/>
-    <row r="733" ht="14.25" customHeight="1"/>
-    <row r="734" ht="14.25" customHeight="1"/>
-    <row r="735" ht="14.25" customHeight="1"/>
-    <row r="736" ht="14.25" customHeight="1"/>
-    <row r="737" ht="14.25" customHeight="1"/>
-    <row r="738" ht="14.25" customHeight="1"/>
-    <row r="739" ht="14.25" customHeight="1"/>
-    <row r="740" ht="14.25" customHeight="1"/>
-    <row r="741" ht="14.25" customHeight="1"/>
-    <row r="742" ht="14.25" customHeight="1"/>
-    <row r="743" ht="14.25" customHeight="1"/>
-    <row r="744" ht="14.25" customHeight="1"/>
-    <row r="745" ht="14.25" customHeight="1"/>
-    <row r="746" ht="14.25" customHeight="1"/>
-    <row r="747" ht="14.25" customHeight="1"/>
-    <row r="748" ht="14.25" customHeight="1"/>
-    <row r="749" ht="14.25" customHeight="1"/>
-    <row r="750" ht="14.25" customHeight="1"/>
-    <row r="751" ht="14.25" customHeight="1"/>
-    <row r="752" ht="14.25" customHeight="1"/>
-    <row r="753" ht="14.25" customHeight="1"/>
-    <row r="754" ht="14.25" customHeight="1"/>
-    <row r="755" ht="14.25" customHeight="1"/>
-    <row r="756" ht="14.25" customHeight="1"/>
-    <row r="757" ht="14.25" customHeight="1"/>
-    <row r="758" ht="14.25" customHeight="1"/>
-    <row r="759" ht="14.25" customHeight="1"/>
-    <row r="760" ht="14.25" customHeight="1"/>
-    <row r="761" ht="14.25" customHeight="1"/>
-    <row r="762" ht="14.25" customHeight="1"/>
-    <row r="763" ht="14.25" customHeight="1"/>
-    <row r="764" ht="14.25" customHeight="1"/>
-    <row r="765" ht="14.25" customHeight="1"/>
-    <row r="766" ht="14.25" customHeight="1"/>
-    <row r="767" ht="14.25" customHeight="1"/>
-    <row r="768" ht="14.25" customHeight="1"/>
-    <row r="769" ht="14.25" customHeight="1"/>
-    <row r="770" ht="14.25" customHeight="1"/>
-    <row r="771" ht="14.25" customHeight="1"/>
-    <row r="772" ht="14.25" customHeight="1"/>
-    <row r="773" ht="14.25" customHeight="1"/>
-    <row r="774" ht="14.25" customHeight="1"/>
-    <row r="775" ht="14.25" customHeight="1"/>
-    <row r="776" ht="14.25" customHeight="1"/>
-    <row r="777" ht="14.25" customHeight="1"/>
-    <row r="778" ht="14.25" customHeight="1"/>
-    <row r="779" ht="14.25" customHeight="1"/>
-    <row r="780" ht="14.25" customHeight="1"/>
-    <row r="781" ht="14.25" customHeight="1"/>
-    <row r="782" ht="14.25" customHeight="1"/>
-    <row r="783" ht="14.25" customHeight="1"/>
-    <row r="784" ht="14.25" customHeight="1"/>
-    <row r="785" ht="14.25" customHeight="1"/>
-    <row r="786" ht="14.25" customHeight="1"/>
-    <row r="787" ht="14.25" customHeight="1"/>
-    <row r="788" ht="14.25" customHeight="1"/>
-    <row r="789" ht="14.25" customHeight="1"/>
-    <row r="790" ht="14.25" customHeight="1"/>
-    <row r="791" ht="14.25" customHeight="1"/>
-    <row r="792" ht="14.25" customHeight="1"/>
-    <row r="793" ht="14.25" customHeight="1"/>
-    <row r="794" ht="14.25" customHeight="1"/>
-    <row r="795" ht="14.25" customHeight="1"/>
-    <row r="796" ht="14.25" customHeight="1"/>
-    <row r="797" ht="14.25" customHeight="1"/>
-    <row r="798" ht="14.25" customHeight="1"/>
-    <row r="799" ht="14.25" customHeight="1"/>
-    <row r="800" ht="14.25" customHeight="1"/>
-    <row r="801" ht="14.25" customHeight="1"/>
-    <row r="802" ht="14.25" customHeight="1"/>
-    <row r="803" ht="14.25" customHeight="1"/>
-    <row r="804" ht="14.25" customHeight="1"/>
-    <row r="805" ht="14.25" customHeight="1"/>
-    <row r="806" ht="14.25" customHeight="1"/>
-    <row r="807" ht="14.25" customHeight="1"/>
-    <row r="808" ht="14.25" customHeight="1"/>
-    <row r="809" ht="14.25" customHeight="1"/>
-    <row r="810" ht="14.25" customHeight="1"/>
-    <row r="811" ht="14.25" customHeight="1"/>
-    <row r="812" ht="14.25" customHeight="1"/>
-    <row r="813" ht="14.25" customHeight="1"/>
-    <row r="814" ht="14.25" customHeight="1"/>
-    <row r="815" ht="14.25" customHeight="1"/>
-    <row r="816" ht="14.25" customHeight="1"/>
-    <row r="817" ht="14.25" customHeight="1"/>
-    <row r="818" ht="14.25" customHeight="1"/>
-    <row r="819" ht="14.25" customHeight="1"/>
-    <row r="820" ht="14.25" customHeight="1"/>
-    <row r="821" ht="14.25" customHeight="1"/>
-    <row r="822" ht="14.25" customHeight="1"/>
-    <row r="823" ht="14.25" customHeight="1"/>
-    <row r="824" ht="14.25" customHeight="1"/>
-    <row r="825" ht="14.25" customHeight="1"/>
-    <row r="826" ht="14.25" customHeight="1"/>
-    <row r="827" ht="14.25" customHeight="1"/>
-    <row r="828" ht="14.25" customHeight="1"/>
-    <row r="829" ht="14.25" customHeight="1"/>
-    <row r="830" ht="14.25" customHeight="1"/>
-    <row r="831" ht="14.25" customHeight="1"/>
-    <row r="832" ht="14.25" customHeight="1"/>
-    <row r="833" ht="14.25" customHeight="1"/>
-    <row r="834" ht="14.25" customHeight="1"/>
-    <row r="835" ht="14.25" customHeight="1"/>
-    <row r="836" ht="14.25" customHeight="1"/>
-    <row r="837" ht="14.25" customHeight="1"/>
-    <row r="838" ht="14.25" customHeight="1"/>
-    <row r="839" ht="14.25" customHeight="1"/>
-    <row r="840" ht="14.25" customHeight="1"/>
-    <row r="841" ht="14.25" customHeight="1"/>
-    <row r="842" ht="14.25" customHeight="1"/>
-    <row r="843" ht="14.25" customHeight="1"/>
-    <row r="844" ht="14.25" customHeight="1"/>
-    <row r="845" ht="14.25" customHeight="1"/>
-    <row r="846" ht="14.25" customHeight="1"/>
-    <row r="847" ht="14.25" customHeight="1"/>
-    <row r="848" ht="14.25" customHeight="1"/>
-    <row r="849" ht="14.25" customHeight="1"/>
-    <row r="850" ht="14.25" customHeight="1"/>
-    <row r="851" ht="14.25" customHeight="1"/>
-    <row r="852" ht="14.25" customHeight="1"/>
-    <row r="853" ht="14.25" customHeight="1"/>
-    <row r="854" ht="14.25" customHeight="1"/>
-    <row r="855" ht="14.25" customHeight="1"/>
-    <row r="856" ht="14.25" customHeight="1"/>
-    <row r="857" ht="14.25" customHeight="1"/>
-    <row r="858" ht="14.25" customHeight="1"/>
-    <row r="859" ht="14.25" customHeight="1"/>
-    <row r="860" ht="14.25" customHeight="1"/>
-    <row r="861" ht="14.25" customHeight="1"/>
-    <row r="862" ht="14.25" customHeight="1"/>
-    <row r="863" ht="14.25" customHeight="1"/>
-    <row r="864" ht="14.25" customHeight="1"/>
-    <row r="865" ht="14.25" customHeight="1"/>
-    <row r="866" ht="14.25" customHeight="1"/>
-    <row r="867" ht="14.25" customHeight="1"/>
-    <row r="868" ht="14.25" customHeight="1"/>
-    <row r="869" ht="14.25" customHeight="1"/>
-    <row r="870" ht="14.25" customHeight="1"/>
-    <row r="871" ht="14.25" customHeight="1"/>
-    <row r="872" ht="14.25" customHeight="1"/>
-    <row r="873" ht="14.25" customHeight="1"/>
-    <row r="874" ht="14.25" customHeight="1"/>
-    <row r="875" ht="14.25" customHeight="1"/>
-    <row r="876" ht="14.25" customHeight="1"/>
-    <row r="877" ht="14.25" customHeight="1"/>
-    <row r="878" ht="14.25" customHeight="1"/>
-    <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
-    <row r="989" ht="14.25" customHeight="1"/>
-    <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
-    <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid ABRA\Documents\UiPath\PerformerProjet1LRE\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpa.lre.res.dev\Documents\UiPath\PerformerProjet1LRE\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FD107F-504D-46BE-A9E4-C156996EEEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="38700" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="13815" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="171">
   <si>
     <t>Name</t>
   </si>
@@ -120,9 +119,6 @@
     <t>OrchestratorQueueFolder</t>
   </si>
   <si>
-    <t>Folder name. The value must match a folder defined in Orchestrator and queue specified as OrchestratorQueueName should be created in this folder. For classic folders leave the value field empty.</t>
-  </si>
-  <si>
     <t>MaxConsecutiveSystemExceptions</t>
   </si>
   <si>
@@ -177,18 +173,51 @@
     <t>SGFD/LRE-RES</t>
   </si>
   <si>
+    <t>Chemin du dossier contenant les fichiers PDF en entrée</t>
+  </si>
+  <si>
+    <t>Chemin du dossier où seront stockés les fichiers traités par le robot</t>
+  </si>
+  <si>
+    <t>Chemin du dossier réseau de destination pour le fichier ZIP généré et le XML de consolidation.</t>
+  </si>
+  <si>
+    <t>Chemin du dossier ou se traite le dossier en cours</t>
+  </si>
+  <si>
     <t>pdfQueue</t>
   </si>
   <si>
+    <t>DossierEncours</t>
+  </si>
+  <si>
+    <t>DossierRejet</t>
+  </si>
+  <si>
+    <t>DossierEntree</t>
+  </si>
+  <si>
+    <t>DossierTraitees</t>
+  </si>
+  <si>
+    <t>DossierSortie</t>
+  </si>
+  <si>
     <t>folderReport</t>
   </si>
   <si>
+    <t>DossierRapport</t>
+  </si>
+  <si>
     <t>Destinataire</t>
   </si>
   <si>
     <t>folderPathTmp</t>
   </si>
   <si>
+    <t>DossierTemporaire</t>
+  </si>
+  <si>
     <t>BE001</t>
   </si>
   <si>
@@ -219,12 +248,54 @@
     <t>BE013</t>
   </si>
   <si>
+    <t>Chemin du dossier où seront stockés les fichiers que le robot ne pourra pas traiter</t>
+  </si>
+  <si>
     <t>bodyMessage</t>
   </si>
   <si>
+    <t>Chemin du dossier où seront stockés les rapports</t>
+  </si>
+  <si>
     <t>Le destinataire du mail d'erreur</t>
   </si>
   <si>
+    <t>Chemin du dossier où seront stockés les fichiers qui seront zippé</t>
+  </si>
+  <si>
+    <t>Id ou MDP windows KO</t>
+  </si>
+  <si>
+    <t>Accès aux données d’entrées impossible</t>
+  </si>
+  <si>
+    <t>Données d’entrées absentes</t>
+  </si>
+  <si>
+    <t>Accès au template impossible</t>
+  </si>
+  <si>
+    <t>Excel KO</t>
+  </si>
+  <si>
+    <t>Accès au dossier pour le dépôt impossible</t>
+  </si>
+  <si>
+    <t>Outlook KO</t>
+  </si>
+  <si>
+    <t>Extraction KO/format KO</t>
+  </si>
+  <si>
+    <t>Hors périmètre</t>
+  </si>
+  <si>
+    <t>Existence de plusieurs réferences dans une seule page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LE corps du mail à envoyer au destinataire en cas d'erreur </t>
+  </si>
+  <si>
     <t>CorpsMail</t>
   </si>
   <si>
@@ -237,6 +308,9 @@
     <t>BE008</t>
   </si>
   <si>
+    <t>Dossier introuvable</t>
+  </si>
+  <si>
     <t>bodyBE001</t>
   </si>
   <si>
@@ -384,6 +458,9 @@
     <t>BE099Objet</t>
   </si>
   <si>
+    <t>Erreur Inconnue</t>
+  </si>
+  <si>
     <t>NomRapportMensuel</t>
   </si>
   <si>
@@ -435,41 +512,38 @@
     <t>LRE Performer</t>
   </si>
   <si>
-    <t>wabra@silamir.com</t>
-  </si>
-  <si>
-    <t>motcle</t>
-  </si>
-  <si>
-    <t>Intercalaire</t>
-  </si>
-  <si>
-    <t>C:\Users\Walid ABRA\Documents\TEST\1</t>
-  </si>
-  <si>
-    <t>C:\Users\Walid ABRA\Documents\TEST\2</t>
-  </si>
-  <si>
-    <t>C:\Users\Walid ABRA\Documents\TEST\3</t>
-  </si>
-  <si>
-    <t>C:\Users\Walid ABRA\Documents\TEST\4</t>
-  </si>
-  <si>
-    <t>C:\Users\Walid ABRA\Documents\TEST\5</t>
-  </si>
-  <si>
-    <t>C:\Users\Walid ABRA\Documents\TEST\6</t>
-  </si>
-  <si>
-    <t>C:\Users\Walid ABRA\Documents\TEST\7</t>
+    <t>BE014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clé num soc KO </t>
+  </si>
+  <si>
+    <t>bodyBE014</t>
+  </si>
+  <si>
+    <t>BE014Corps</t>
+  </si>
+  <si>
+    <t>objectBE014</t>
+  </si>
+  <si>
+    <t>BE014Objet</t>
+  </si>
+  <si>
+    <t>Folder name. The value must match a folder defined in Orchestrator and queue specified as OrchestratorQueueName should be created in this folder. For classic folders leave the value field empty. SGFD/LRE-RES</t>
+  </si>
+  <si>
+    <t>NameZip</t>
+  </si>
+  <si>
+    <t>MATMUTRPA_RE7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -493,12 +567,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -517,11 +585,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -531,10 +598,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -846,7 +911,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z998"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -895,7 +960,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -907,7 +972,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
@@ -916,7 +981,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>22</v>
@@ -925,10 +990,10 @@
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
@@ -1930,8 +1995,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z970"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z968"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -1987,13 +2052,13 @@
     </row>
     <row r="3" spans="1:26" ht="45">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
@@ -2066,1496 +2131,135 @@
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="17" spans="1:3" ht="45">
+      <c r="A17" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" spans="1:4" ht="45">
-      <c r="A17" t="s">
-        <v>39</v>
       </c>
       <c r="B17" t="b">
         <v>0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="14.25" customHeight="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="14.25" customHeight="1">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="14.25" customHeight="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="14.25" customHeight="1">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="14.25" customHeight="1">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="14.25" customHeight="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="14.25" customHeight="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="14.25" customHeight="1">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="14.25" customHeight="1">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="14.25" customHeight="1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="14.25" customHeight="1">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="14.25" customHeight="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="14.25" customHeight="1">
       <c r="A26" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="14.25" customHeight="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1">
       <c r="A27" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C27" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A28" t="s">
-        <v>137</v>
-      </c>
-      <c r="B28" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A29" t="s">
-        <v>138</v>
-      </c>
-      <c r="B29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A30" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A33" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A34" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A35" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A36" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A37" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A38" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A39" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A40" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A41" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A42" t="s">
-        <v>59</v>
-      </c>
-      <c r="B42" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A43" t="s">
-        <v>60</v>
-      </c>
-      <c r="B43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A44" t="s">
-        <v>69</v>
-      </c>
-      <c r="B44" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A45" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A46" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A47" t="s">
-        <v>63</v>
-      </c>
-      <c r="B47" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A48" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B48" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A49" t="s">
-        <v>64</v>
-      </c>
-      <c r="B49" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A50" t="s">
-        <v>67</v>
-      </c>
-      <c r="B50" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A51" t="s">
-        <v>70</v>
-      </c>
-      <c r="B51" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A52" t="s">
-        <v>71</v>
-      </c>
-      <c r="B52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A53" t="s">
-        <v>72</v>
-      </c>
-      <c r="B53" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A54" t="s">
-        <v>73</v>
-      </c>
-      <c r="B54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A55" t="s">
-        <v>74</v>
-      </c>
-      <c r="B55" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A56" t="s">
-        <v>75</v>
-      </c>
-      <c r="B56" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A57" t="s">
-        <v>76</v>
-      </c>
-      <c r="B57" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A58" t="s">
-        <v>77</v>
-      </c>
-      <c r="B58" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A59" t="s">
-        <v>78</v>
-      </c>
-      <c r="B59" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A60" t="s">
-        <v>79</v>
-      </c>
-      <c r="B60" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A61" t="s">
-        <v>80</v>
-      </c>
-      <c r="B61" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A62" t="s">
-        <v>81</v>
-      </c>
-      <c r="B62" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A63" t="s">
-        <v>95</v>
-      </c>
-      <c r="B63" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A64" t="s">
-        <v>96</v>
-      </c>
-      <c r="B64" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A65" t="s">
-        <v>97</v>
-      </c>
-      <c r="B65" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A66" t="s">
-        <v>98</v>
-      </c>
-      <c r="B66" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A67" t="s">
-        <v>99</v>
-      </c>
-      <c r="B67" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A68" t="s">
-        <v>100</v>
-      </c>
-      <c r="B68" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A69" t="s">
-        <v>101</v>
-      </c>
-      <c r="B69" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A70" t="s">
-        <v>102</v>
-      </c>
-      <c r="B70" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A71" t="s">
-        <v>103</v>
-      </c>
-      <c r="B71" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A72" t="s">
-        <v>104</v>
-      </c>
-      <c r="B72" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A73" t="s">
-        <v>105</v>
-      </c>
-      <c r="B73" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A74" t="s">
-        <v>117</v>
-      </c>
-      <c r="B74" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="76" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="77" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="78" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="79" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="80" spans="1:2" ht="14.25" customHeight="1"/>
-    <row r="81" ht="14.25" customHeight="1"/>
-    <row r="82" ht="14.25" customHeight="1"/>
-    <row r="83" ht="14.25" customHeight="1"/>
-    <row r="84" ht="14.25" customHeight="1"/>
-    <row r="85" ht="14.25" customHeight="1"/>
-    <row r="86" ht="14.25" customHeight="1"/>
-    <row r="87" ht="14.25" customHeight="1"/>
-    <row r="88" ht="14.25" customHeight="1"/>
-    <row r="89" ht="14.25" customHeight="1"/>
-    <row r="90" ht="14.25" customHeight="1"/>
-    <row r="91" ht="14.25" customHeight="1"/>
-    <row r="92" ht="14.25" customHeight="1"/>
-    <row r="93" ht="14.25" customHeight="1"/>
-    <row r="94" ht="14.25" customHeight="1"/>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
-    <row r="97" ht="14.25" customHeight="1"/>
-    <row r="98" ht="14.25" customHeight="1"/>
-    <row r="99" ht="14.25" customHeight="1"/>
-    <row r="100" ht="14.25" customHeight="1"/>
-    <row r="101" ht="14.25" customHeight="1"/>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
-    <row r="112" ht="14.25" customHeight="1"/>
-    <row r="113" ht="14.25" customHeight="1"/>
-    <row r="114" ht="14.25" customHeight="1"/>
-    <row r="115" ht="14.25" customHeight="1"/>
-    <row r="116" ht="14.25" customHeight="1"/>
-    <row r="117" ht="14.25" customHeight="1"/>
-    <row r="118" ht="14.25" customHeight="1"/>
-    <row r="119" ht="14.25" customHeight="1"/>
-    <row r="120" ht="14.25" customHeight="1"/>
-    <row r="121" ht="14.25" customHeight="1"/>
-    <row r="122" ht="14.25" customHeight="1"/>
-    <row r="123" ht="14.25" customHeight="1"/>
-    <row r="124" ht="14.25" customHeight="1"/>
-    <row r="125" ht="14.25" customHeight="1"/>
-    <row r="126" ht="14.25" customHeight="1"/>
-    <row r="127" ht="14.25" customHeight="1"/>
-    <row r="128" ht="14.25" customHeight="1"/>
-    <row r="129" ht="14.25" customHeight="1"/>
-    <row r="130" ht="14.25" customHeight="1"/>
-    <row r="131" ht="14.25" customHeight="1"/>
-    <row r="132" ht="14.25" customHeight="1"/>
-    <row r="133" ht="14.25" customHeight="1"/>
-    <row r="134" ht="14.25" customHeight="1"/>
-    <row r="135" ht="14.25" customHeight="1"/>
-    <row r="136" ht="14.25" customHeight="1"/>
-    <row r="137" ht="14.25" customHeight="1"/>
-    <row r="138" ht="14.25" customHeight="1"/>
-    <row r="139" ht="14.25" customHeight="1"/>
-    <row r="140" ht="14.25" customHeight="1"/>
-    <row r="141" ht="14.25" customHeight="1"/>
-    <row r="142" ht="14.25" customHeight="1"/>
-    <row r="143" ht="14.25" customHeight="1"/>
-    <row r="144" ht="14.25" customHeight="1"/>
-    <row r="145" ht="14.25" customHeight="1"/>
-    <row r="146" ht="14.25" customHeight="1"/>
-    <row r="147" ht="14.25" customHeight="1"/>
-    <row r="148" ht="14.25" customHeight="1"/>
-    <row r="149" ht="14.25" customHeight="1"/>
-    <row r="150" ht="14.25" customHeight="1"/>
-    <row r="151" ht="14.25" customHeight="1"/>
-    <row r="152" ht="14.25" customHeight="1"/>
-    <row r="153" ht="14.25" customHeight="1"/>
-    <row r="154" ht="14.25" customHeight="1"/>
-    <row r="155" ht="14.25" customHeight="1"/>
-    <row r="156" ht="14.25" customHeight="1"/>
-    <row r="157" ht="14.25" customHeight="1"/>
-    <row r="158" ht="14.25" customHeight="1"/>
-    <row r="159" ht="14.25" customHeight="1"/>
-    <row r="160" ht="14.25" customHeight="1"/>
-    <row r="161" ht="14.25" customHeight="1"/>
-    <row r="162" ht="14.25" customHeight="1"/>
-    <row r="163" ht="14.25" customHeight="1"/>
-    <row r="164" ht="14.25" customHeight="1"/>
-    <row r="165" ht="14.25" customHeight="1"/>
-    <row r="166" ht="14.25" customHeight="1"/>
-    <row r="167" ht="14.25" customHeight="1"/>
-    <row r="168" ht="14.25" customHeight="1"/>
-    <row r="169" ht="14.25" customHeight="1"/>
-    <row r="170" ht="14.25" customHeight="1"/>
-    <row r="171" ht="14.25" customHeight="1"/>
-    <row r="172" ht="14.25" customHeight="1"/>
-    <row r="173" ht="14.25" customHeight="1"/>
-    <row r="174" ht="14.25" customHeight="1"/>
-    <row r="175" ht="14.25" customHeight="1"/>
-    <row r="176" ht="14.25" customHeight="1"/>
-    <row r="177" ht="14.25" customHeight="1"/>
-    <row r="178" ht="14.25" customHeight="1"/>
-    <row r="179" ht="14.25" customHeight="1"/>
-    <row r="180" ht="14.25" customHeight="1"/>
-    <row r="181" ht="14.25" customHeight="1"/>
-    <row r="182" ht="14.25" customHeight="1"/>
-    <row r="183" ht="14.25" customHeight="1"/>
-    <row r="184" ht="14.25" customHeight="1"/>
-    <row r="185" ht="14.25" customHeight="1"/>
-    <row r="186" ht="14.25" customHeight="1"/>
-    <row r="187" ht="14.25" customHeight="1"/>
-    <row r="188" ht="14.25" customHeight="1"/>
-    <row r="189" ht="14.25" customHeight="1"/>
-    <row r="190" ht="14.25" customHeight="1"/>
-    <row r="191" ht="14.25" customHeight="1"/>
-    <row r="192" ht="14.25" customHeight="1"/>
-    <row r="193" ht="14.25" customHeight="1"/>
-    <row r="194" ht="14.25" customHeight="1"/>
-    <row r="195" ht="14.25" customHeight="1"/>
-    <row r="196" ht="14.25" customHeight="1"/>
-    <row r="197" ht="14.25" customHeight="1"/>
-    <row r="198" ht="14.25" customHeight="1"/>
-    <row r="199" ht="14.25" customHeight="1"/>
-    <row r="200" ht="14.25" customHeight="1"/>
-    <row r="201" ht="14.25" customHeight="1"/>
-    <row r="202" ht="14.25" customHeight="1"/>
-    <row r="203" ht="14.25" customHeight="1"/>
-    <row r="204" ht="14.25" customHeight="1"/>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
-    <row r="209" ht="14.25" customHeight="1"/>
-    <row r="210" ht="14.25" customHeight="1"/>
-    <row r="211" ht="14.25" customHeight="1"/>
-    <row r="212" ht="14.25" customHeight="1"/>
-    <row r="213" ht="14.25" customHeight="1"/>
-    <row r="214" ht="14.25" customHeight="1"/>
-    <row r="215" ht="14.25" customHeight="1"/>
-    <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
-    <row r="219" ht="14.25" customHeight="1"/>
-    <row r="220" ht="14.25" customHeight="1"/>
-    <row r="221" ht="14.25" customHeight="1"/>
-    <row r="222" ht="14.25" customHeight="1"/>
-    <row r="223" ht="14.25" customHeight="1"/>
-    <row r="224" ht="14.25" customHeight="1"/>
-    <row r="225" ht="14.25" customHeight="1"/>
-    <row r="226" ht="14.25" customHeight="1"/>
-    <row r="227" ht="14.25" customHeight="1"/>
-    <row r="228" ht="14.25" customHeight="1"/>
-    <row r="229" ht="14.25" customHeight="1"/>
-    <row r="230" ht="14.25" customHeight="1"/>
-    <row r="231" ht="14.25" customHeight="1"/>
-    <row r="232" ht="14.25" customHeight="1"/>
-    <row r="233" ht="14.25" customHeight="1"/>
-    <row r="234" ht="14.25" customHeight="1"/>
-    <row r="235" ht="14.25" customHeight="1"/>
-    <row r="236" ht="14.25" customHeight="1"/>
-    <row r="237" ht="14.25" customHeight="1"/>
-    <row r="238" ht="14.25" customHeight="1"/>
-    <row r="239" ht="14.25" customHeight="1"/>
-    <row r="240" ht="14.25" customHeight="1"/>
-    <row r="241" ht="14.25" customHeight="1"/>
-    <row r="242" ht="14.25" customHeight="1"/>
-    <row r="243" ht="14.25" customHeight="1"/>
-    <row r="244" ht="14.25" customHeight="1"/>
-    <row r="245" ht="14.25" customHeight="1"/>
-    <row r="246" ht="14.25" customHeight="1"/>
-    <row r="247" ht="14.25" customHeight="1"/>
-    <row r="248" ht="14.25" customHeight="1"/>
-    <row r="249" ht="14.25" customHeight="1"/>
-    <row r="250" ht="14.25" customHeight="1"/>
-    <row r="251" ht="14.25" customHeight="1"/>
-    <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="14.25" customHeight="1"/>
-    <row r="254" ht="14.25" customHeight="1"/>
-    <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="14.25" customHeight="1"/>
-    <row r="257" ht="14.25" customHeight="1"/>
-    <row r="258" ht="14.25" customHeight="1"/>
-    <row r="259" ht="14.25" customHeight="1"/>
-    <row r="260" ht="14.25" customHeight="1"/>
-    <row r="261" ht="14.25" customHeight="1"/>
-    <row r="262" ht="14.25" customHeight="1"/>
-    <row r="263" ht="14.25" customHeight="1"/>
-    <row r="264" ht="14.25" customHeight="1"/>
-    <row r="265" ht="14.25" customHeight="1"/>
-    <row r="266" ht="14.25" customHeight="1"/>
-    <row r="267" ht="14.25" customHeight="1"/>
-    <row r="268" ht="14.25" customHeight="1"/>
-    <row r="269" ht="14.25" customHeight="1"/>
-    <row r="270" ht="14.25" customHeight="1"/>
-    <row r="271" ht="14.25" customHeight="1"/>
-    <row r="272" ht="14.25" customHeight="1"/>
-    <row r="273" ht="14.25" customHeight="1"/>
-    <row r="274" ht="14.25" customHeight="1"/>
-    <row r="275" ht="14.25" customHeight="1"/>
-    <row r="276" ht="14.25" customHeight="1"/>
-    <row r="277" ht="14.25" customHeight="1"/>
-    <row r="278" ht="14.25" customHeight="1"/>
-    <row r="279" ht="14.25" customHeight="1"/>
-    <row r="280" ht="14.25" customHeight="1"/>
-    <row r="281" ht="14.25" customHeight="1"/>
-    <row r="282" ht="14.25" customHeight="1"/>
-    <row r="283" ht="14.25" customHeight="1"/>
-    <row r="284" ht="14.25" customHeight="1"/>
-    <row r="285" ht="14.25" customHeight="1"/>
-    <row r="286" ht="14.25" customHeight="1"/>
-    <row r="287" ht="14.25" customHeight="1"/>
-    <row r="288" ht="14.25" customHeight="1"/>
-    <row r="289" ht="14.25" customHeight="1"/>
-    <row r="290" ht="14.25" customHeight="1"/>
-    <row r="291" ht="14.25" customHeight="1"/>
-    <row r="292" ht="14.25" customHeight="1"/>
-    <row r="293" ht="14.25" customHeight="1"/>
-    <row r="294" ht="14.25" customHeight="1"/>
-    <row r="295" ht="14.25" customHeight="1"/>
-    <row r="296" ht="14.25" customHeight="1"/>
-    <row r="297" ht="14.25" customHeight="1"/>
-    <row r="298" ht="14.25" customHeight="1"/>
-    <row r="299" ht="14.25" customHeight="1"/>
-    <row r="300" ht="14.25" customHeight="1"/>
-    <row r="301" ht="14.25" customHeight="1"/>
-    <row r="302" ht="14.25" customHeight="1"/>
-    <row r="303" ht="14.25" customHeight="1"/>
-    <row r="304" ht="14.25" customHeight="1"/>
-    <row r="305" ht="14.25" customHeight="1"/>
-    <row r="306" ht="14.25" customHeight="1"/>
-    <row r="307" ht="14.25" customHeight="1"/>
-    <row r="308" ht="14.25" customHeight="1"/>
-    <row r="309" ht="14.25" customHeight="1"/>
-    <row r="310" ht="14.25" customHeight="1"/>
-    <row r="311" ht="14.25" customHeight="1"/>
-    <row r="312" ht="14.25" customHeight="1"/>
-    <row r="313" ht="14.25" customHeight="1"/>
-    <row r="314" ht="14.25" customHeight="1"/>
-    <row r="315" ht="14.25" customHeight="1"/>
-    <row r="316" ht="14.25" customHeight="1"/>
-    <row r="317" ht="14.25" customHeight="1"/>
-    <row r="318" ht="14.25" customHeight="1"/>
-    <row r="319" ht="14.25" customHeight="1"/>
-    <row r="320" ht="14.25" customHeight="1"/>
-    <row r="321" ht="14.25" customHeight="1"/>
-    <row r="322" ht="14.25" customHeight="1"/>
-    <row r="323" ht="14.25" customHeight="1"/>
-    <row r="324" ht="14.25" customHeight="1"/>
-    <row r="325" ht="14.25" customHeight="1"/>
-    <row r="326" ht="14.25" customHeight="1"/>
-    <row r="327" ht="14.25" customHeight="1"/>
-    <row r="328" ht="14.25" customHeight="1"/>
-    <row r="329" ht="14.25" customHeight="1"/>
-    <row r="330" ht="14.25" customHeight="1"/>
-    <row r="331" ht="14.25" customHeight="1"/>
-    <row r="332" ht="14.25" customHeight="1"/>
-    <row r="333" ht="14.25" customHeight="1"/>
-    <row r="334" ht="14.25" customHeight="1"/>
-    <row r="335" ht="14.25" customHeight="1"/>
-    <row r="336" ht="14.25" customHeight="1"/>
-    <row r="337" ht="14.25" customHeight="1"/>
-    <row r="338" ht="14.25" customHeight="1"/>
-    <row r="339" ht="14.25" customHeight="1"/>
-    <row r="340" ht="14.25" customHeight="1"/>
-    <row r="341" ht="14.25" customHeight="1"/>
-    <row r="342" ht="14.25" customHeight="1"/>
-    <row r="343" ht="14.25" customHeight="1"/>
-    <row r="344" ht="14.25" customHeight="1"/>
-    <row r="345" ht="14.25" customHeight="1"/>
-    <row r="346" ht="14.25" customHeight="1"/>
-    <row r="347" ht="14.25" customHeight="1"/>
-    <row r="348" ht="14.25" customHeight="1"/>
-    <row r="349" ht="14.25" customHeight="1"/>
-    <row r="350" ht="14.25" customHeight="1"/>
-    <row r="351" ht="14.25" customHeight="1"/>
-    <row r="352" ht="14.25" customHeight="1"/>
-    <row r="353" ht="14.25" customHeight="1"/>
-    <row r="354" ht="14.25" customHeight="1"/>
-    <row r="355" ht="14.25" customHeight="1"/>
-    <row r="356" ht="14.25" customHeight="1"/>
-    <row r="357" ht="14.25" customHeight="1"/>
-    <row r="358" ht="14.25" customHeight="1"/>
-    <row r="359" ht="14.25" customHeight="1"/>
-    <row r="360" ht="14.25" customHeight="1"/>
-    <row r="361" ht="14.25" customHeight="1"/>
-    <row r="362" ht="14.25" customHeight="1"/>
-    <row r="363" ht="14.25" customHeight="1"/>
-    <row r="364" ht="14.25" customHeight="1"/>
-    <row r="365" ht="14.25" customHeight="1"/>
-    <row r="366" ht="14.25" customHeight="1"/>
-    <row r="367" ht="14.25" customHeight="1"/>
-    <row r="368" ht="14.25" customHeight="1"/>
-    <row r="369" ht="14.25" customHeight="1"/>
-    <row r="370" ht="14.25" customHeight="1"/>
-    <row r="371" ht="14.25" customHeight="1"/>
-    <row r="372" ht="14.25" customHeight="1"/>
-    <row r="373" ht="14.25" customHeight="1"/>
-    <row r="374" ht="14.25" customHeight="1"/>
-    <row r="375" ht="14.25" customHeight="1"/>
-    <row r="376" ht="14.25" customHeight="1"/>
-    <row r="377" ht="14.25" customHeight="1"/>
-    <row r="378" ht="14.25" customHeight="1"/>
-    <row r="379" ht="14.25" customHeight="1"/>
-    <row r="380" ht="14.25" customHeight="1"/>
-    <row r="381" ht="14.25" customHeight="1"/>
-    <row r="382" ht="14.25" customHeight="1"/>
-    <row r="383" ht="14.25" customHeight="1"/>
-    <row r="384" ht="14.25" customHeight="1"/>
-    <row r="385" ht="14.25" customHeight="1"/>
-    <row r="386" ht="14.25" customHeight="1"/>
-    <row r="387" ht="14.25" customHeight="1"/>
-    <row r="388" ht="14.25" customHeight="1"/>
-    <row r="389" ht="14.25" customHeight="1"/>
-    <row r="390" ht="14.25" customHeight="1"/>
-    <row r="391" ht="14.25" customHeight="1"/>
-    <row r="392" ht="14.25" customHeight="1"/>
-    <row r="393" ht="14.25" customHeight="1"/>
-    <row r="394" ht="14.25" customHeight="1"/>
-    <row r="395" ht="14.25" customHeight="1"/>
-    <row r="396" ht="14.25" customHeight="1"/>
-    <row r="397" ht="14.25" customHeight="1"/>
-    <row r="398" ht="14.25" customHeight="1"/>
-    <row r="399" ht="14.25" customHeight="1"/>
-    <row r="400" ht="14.25" customHeight="1"/>
-    <row r="401" ht="14.25" customHeight="1"/>
-    <row r="402" ht="14.25" customHeight="1"/>
-    <row r="403" ht="14.25" customHeight="1"/>
-    <row r="404" ht="14.25" customHeight="1"/>
-    <row r="405" ht="14.25" customHeight="1"/>
-    <row r="406" ht="14.25" customHeight="1"/>
-    <row r="407" ht="14.25" customHeight="1"/>
-    <row r="408" ht="14.25" customHeight="1"/>
-    <row r="409" ht="14.25" customHeight="1"/>
-    <row r="410" ht="14.25" customHeight="1"/>
-    <row r="411" ht="14.25" customHeight="1"/>
-    <row r="412" ht="14.25" customHeight="1"/>
-    <row r="413" ht="14.25" customHeight="1"/>
-    <row r="414" ht="14.25" customHeight="1"/>
-    <row r="415" ht="14.25" customHeight="1"/>
-    <row r="416" ht="14.25" customHeight="1"/>
-    <row r="417" ht="14.25" customHeight="1"/>
-    <row r="418" ht="14.25" customHeight="1"/>
-    <row r="419" ht="14.25" customHeight="1"/>
-    <row r="420" ht="14.25" customHeight="1"/>
-    <row r="421" ht="14.25" customHeight="1"/>
-    <row r="422" ht="14.25" customHeight="1"/>
-    <row r="423" ht="14.25" customHeight="1"/>
-    <row r="424" ht="14.25" customHeight="1"/>
-    <row r="425" ht="14.25" customHeight="1"/>
-    <row r="426" ht="14.25" customHeight="1"/>
-    <row r="427" ht="14.25" customHeight="1"/>
-    <row r="428" ht="14.25" customHeight="1"/>
-    <row r="429" ht="14.25" customHeight="1"/>
-    <row r="430" ht="14.25" customHeight="1"/>
-    <row r="431" ht="14.25" customHeight="1"/>
-    <row r="432" ht="14.25" customHeight="1"/>
-    <row r="433" ht="14.25" customHeight="1"/>
-    <row r="434" ht="14.25" customHeight="1"/>
-    <row r="435" ht="14.25" customHeight="1"/>
-    <row r="436" ht="14.25" customHeight="1"/>
-    <row r="437" ht="14.25" customHeight="1"/>
-    <row r="438" ht="14.25" customHeight="1"/>
-    <row r="439" ht="14.25" customHeight="1"/>
-    <row r="440" ht="14.25" customHeight="1"/>
-    <row r="441" ht="14.25" customHeight="1"/>
-    <row r="442" ht="14.25" customHeight="1"/>
-    <row r="443" ht="14.25" customHeight="1"/>
-    <row r="444" ht="14.25" customHeight="1"/>
-    <row r="445" ht="14.25" customHeight="1"/>
-    <row r="446" ht="14.25" customHeight="1"/>
-    <row r="447" ht="14.25" customHeight="1"/>
-    <row r="448" ht="14.25" customHeight="1"/>
-    <row r="449" ht="14.25" customHeight="1"/>
-    <row r="450" ht="14.25" customHeight="1"/>
-    <row r="451" ht="14.25" customHeight="1"/>
-    <row r="452" ht="14.25" customHeight="1"/>
-    <row r="453" ht="14.25" customHeight="1"/>
-    <row r="454" ht="14.25" customHeight="1"/>
-    <row r="455" ht="14.25" customHeight="1"/>
-    <row r="456" ht="14.25" customHeight="1"/>
-    <row r="457" ht="14.25" customHeight="1"/>
-    <row r="458" ht="14.25" customHeight="1"/>
-    <row r="459" ht="14.25" customHeight="1"/>
-    <row r="460" ht="14.25" customHeight="1"/>
-    <row r="461" ht="14.25" customHeight="1"/>
-    <row r="462" ht="14.25" customHeight="1"/>
-    <row r="463" ht="14.25" customHeight="1"/>
-    <row r="464" ht="14.25" customHeight="1"/>
-    <row r="465" ht="14.25" customHeight="1"/>
-    <row r="466" ht="14.25" customHeight="1"/>
-    <row r="467" ht="14.25" customHeight="1"/>
-    <row r="468" ht="14.25" customHeight="1"/>
-    <row r="469" ht="14.25" customHeight="1"/>
-    <row r="470" ht="14.25" customHeight="1"/>
-    <row r="471" ht="14.25" customHeight="1"/>
-    <row r="472" ht="14.25" customHeight="1"/>
-    <row r="473" ht="14.25" customHeight="1"/>
-    <row r="474" ht="14.25" customHeight="1"/>
-    <row r="475" ht="14.25" customHeight="1"/>
-    <row r="476" ht="14.25" customHeight="1"/>
-    <row r="477" ht="14.25" customHeight="1"/>
-    <row r="478" ht="14.25" customHeight="1"/>
-    <row r="479" ht="14.25" customHeight="1"/>
-    <row r="480" ht="14.25" customHeight="1"/>
-    <row r="481" ht="14.25" customHeight="1"/>
-    <row r="482" ht="14.25" customHeight="1"/>
-    <row r="483" ht="14.25" customHeight="1"/>
-    <row r="484" ht="14.25" customHeight="1"/>
-    <row r="485" ht="14.25" customHeight="1"/>
-    <row r="486" ht="14.25" customHeight="1"/>
-    <row r="487" ht="14.25" customHeight="1"/>
-    <row r="488" ht="14.25" customHeight="1"/>
-    <row r="489" ht="14.25" customHeight="1"/>
-    <row r="490" ht="14.25" customHeight="1"/>
-    <row r="491" ht="14.25" customHeight="1"/>
-    <row r="492" ht="14.25" customHeight="1"/>
-    <row r="493" ht="14.25" customHeight="1"/>
-    <row r="494" ht="14.25" customHeight="1"/>
-    <row r="495" ht="14.25" customHeight="1"/>
-    <row r="496" ht="14.25" customHeight="1"/>
-    <row r="497" ht="14.25" customHeight="1"/>
-    <row r="498" ht="14.25" customHeight="1"/>
-    <row r="499" ht="14.25" customHeight="1"/>
-    <row r="500" ht="14.25" customHeight="1"/>
-    <row r="501" ht="14.25" customHeight="1"/>
-    <row r="502" ht="14.25" customHeight="1"/>
-    <row r="503" ht="14.25" customHeight="1"/>
-    <row r="504" ht="14.25" customHeight="1"/>
-    <row r="505" ht="14.25" customHeight="1"/>
-    <row r="506" ht="14.25" customHeight="1"/>
-    <row r="507" ht="14.25" customHeight="1"/>
-    <row r="508" ht="14.25" customHeight="1"/>
-    <row r="509" ht="14.25" customHeight="1"/>
-    <row r="510" ht="14.25" customHeight="1"/>
-    <row r="511" ht="14.25" customHeight="1"/>
-    <row r="512" ht="14.25" customHeight="1"/>
-    <row r="513" ht="14.25" customHeight="1"/>
-    <row r="514" ht="14.25" customHeight="1"/>
-    <row r="515" ht="14.25" customHeight="1"/>
-    <row r="516" ht="14.25" customHeight="1"/>
-    <row r="517" ht="14.25" customHeight="1"/>
-    <row r="518" ht="14.25" customHeight="1"/>
-    <row r="519" ht="14.25" customHeight="1"/>
-    <row r="520" ht="14.25" customHeight="1"/>
-    <row r="521" ht="14.25" customHeight="1"/>
-    <row r="522" ht="14.25" customHeight="1"/>
-    <row r="523" ht="14.25" customHeight="1"/>
-    <row r="524" ht="14.25" customHeight="1"/>
-    <row r="525" ht="14.25" customHeight="1"/>
-    <row r="526" ht="14.25" customHeight="1"/>
-    <row r="527" ht="14.25" customHeight="1"/>
-    <row r="528" ht="14.25" customHeight="1"/>
-    <row r="529" ht="14.25" customHeight="1"/>
-    <row r="530" ht="14.25" customHeight="1"/>
-    <row r="531" ht="14.25" customHeight="1"/>
-    <row r="532" ht="14.25" customHeight="1"/>
-    <row r="533" ht="14.25" customHeight="1"/>
-    <row r="534" ht="14.25" customHeight="1"/>
-    <row r="535" ht="14.25" customHeight="1"/>
-    <row r="536" ht="14.25" customHeight="1"/>
-    <row r="537" ht="14.25" customHeight="1"/>
-    <row r="538" ht="14.25" customHeight="1"/>
-    <row r="539" ht="14.25" customHeight="1"/>
-    <row r="540" ht="14.25" customHeight="1"/>
-    <row r="541" ht="14.25" customHeight="1"/>
-    <row r="542" ht="14.25" customHeight="1"/>
-    <row r="543" ht="14.25" customHeight="1"/>
-    <row r="544" ht="14.25" customHeight="1"/>
-    <row r="545" ht="14.25" customHeight="1"/>
-    <row r="546" ht="14.25" customHeight="1"/>
-    <row r="547" ht="14.25" customHeight="1"/>
-    <row r="548" ht="14.25" customHeight="1"/>
-    <row r="549" ht="14.25" customHeight="1"/>
-    <row r="550" ht="14.25" customHeight="1"/>
-    <row r="551" ht="14.25" customHeight="1"/>
-    <row r="552" ht="14.25" customHeight="1"/>
-    <row r="553" ht="14.25" customHeight="1"/>
-    <row r="554" ht="14.25" customHeight="1"/>
-    <row r="555" ht="14.25" customHeight="1"/>
-    <row r="556" ht="14.25" customHeight="1"/>
-    <row r="557" ht="14.25" customHeight="1"/>
-    <row r="558" ht="14.25" customHeight="1"/>
-    <row r="559" ht="14.25" customHeight="1"/>
-    <row r="560" ht="14.25" customHeight="1"/>
-    <row r="561" ht="14.25" customHeight="1"/>
-    <row r="562" ht="14.25" customHeight="1"/>
-    <row r="563" ht="14.25" customHeight="1"/>
-    <row r="564" ht="14.25" customHeight="1"/>
-    <row r="565" ht="14.25" customHeight="1"/>
-    <row r="566" ht="14.25" customHeight="1"/>
-    <row r="567" ht="14.25" customHeight="1"/>
-    <row r="568" ht="14.25" customHeight="1"/>
-    <row r="569" ht="14.25" customHeight="1"/>
-    <row r="570" ht="14.25" customHeight="1"/>
-    <row r="571" ht="14.25" customHeight="1"/>
-    <row r="572" ht="14.25" customHeight="1"/>
-    <row r="573" ht="14.25" customHeight="1"/>
-    <row r="574" ht="14.25" customHeight="1"/>
-    <row r="575" ht="14.25" customHeight="1"/>
-    <row r="576" ht="14.25" customHeight="1"/>
-    <row r="577" ht="14.25" customHeight="1"/>
-    <row r="578" ht="14.25" customHeight="1"/>
-    <row r="579" ht="14.25" customHeight="1"/>
-    <row r="580" ht="14.25" customHeight="1"/>
-    <row r="581" ht="14.25" customHeight="1"/>
-    <row r="582" ht="14.25" customHeight="1"/>
-    <row r="583" ht="14.25" customHeight="1"/>
-    <row r="584" ht="14.25" customHeight="1"/>
-    <row r="585" ht="14.25" customHeight="1"/>
-    <row r="586" ht="14.25" customHeight="1"/>
-    <row r="587" ht="14.25" customHeight="1"/>
-    <row r="588" ht="14.25" customHeight="1"/>
-    <row r="589" ht="14.25" customHeight="1"/>
-    <row r="590" ht="14.25" customHeight="1"/>
-    <row r="591" ht="14.25" customHeight="1"/>
-    <row r="592" ht="14.25" customHeight="1"/>
-    <row r="593" ht="14.25" customHeight="1"/>
-    <row r="594" ht="14.25" customHeight="1"/>
-    <row r="595" ht="14.25" customHeight="1"/>
-    <row r="596" ht="14.25" customHeight="1"/>
-    <row r="597" ht="14.25" customHeight="1"/>
-    <row r="598" ht="14.25" customHeight="1"/>
-    <row r="599" ht="14.25" customHeight="1"/>
-    <row r="600" ht="14.25" customHeight="1"/>
-    <row r="601" ht="14.25" customHeight="1"/>
-    <row r="602" ht="14.25" customHeight="1"/>
-    <row r="603" ht="14.25" customHeight="1"/>
-    <row r="604" ht="14.25" customHeight="1"/>
-    <row r="605" ht="14.25" customHeight="1"/>
-    <row r="606" ht="14.25" customHeight="1"/>
-    <row r="607" ht="14.25" customHeight="1"/>
-    <row r="608" ht="14.25" customHeight="1"/>
-    <row r="609" ht="14.25" customHeight="1"/>
-    <row r="610" ht="14.25" customHeight="1"/>
-    <row r="611" ht="14.25" customHeight="1"/>
-    <row r="612" ht="14.25" customHeight="1"/>
-    <row r="613" ht="14.25" customHeight="1"/>
-    <row r="614" ht="14.25" customHeight="1"/>
-    <row r="615" ht="14.25" customHeight="1"/>
-    <row r="616" ht="14.25" customHeight="1"/>
-    <row r="617" ht="14.25" customHeight="1"/>
-    <row r="618" ht="14.25" customHeight="1"/>
-    <row r="619" ht="14.25" customHeight="1"/>
-    <row r="620" ht="14.25" customHeight="1"/>
-    <row r="621" ht="14.25" customHeight="1"/>
-    <row r="622" ht="14.25" customHeight="1"/>
-    <row r="623" ht="14.25" customHeight="1"/>
-    <row r="624" ht="14.25" customHeight="1"/>
-    <row r="625" ht="14.25" customHeight="1"/>
-    <row r="626" ht="14.25" customHeight="1"/>
-    <row r="627" ht="14.25" customHeight="1"/>
-    <row r="628" ht="14.25" customHeight="1"/>
-    <row r="629" ht="14.25" customHeight="1"/>
-    <row r="630" ht="14.25" customHeight="1"/>
-    <row r="631" ht="14.25" customHeight="1"/>
-    <row r="632" ht="14.25" customHeight="1"/>
-    <row r="633" ht="14.25" customHeight="1"/>
-    <row r="634" ht="14.25" customHeight="1"/>
-    <row r="635" ht="14.25" customHeight="1"/>
-    <row r="636" ht="14.25" customHeight="1"/>
-    <row r="637" ht="14.25" customHeight="1"/>
-    <row r="638" ht="14.25" customHeight="1"/>
-    <row r="639" ht="14.25" customHeight="1"/>
-    <row r="640" ht="14.25" customHeight="1"/>
-    <row r="641" ht="14.25" customHeight="1"/>
-    <row r="642" ht="14.25" customHeight="1"/>
-    <row r="643" ht="14.25" customHeight="1"/>
-    <row r="644" ht="14.25" customHeight="1"/>
-    <row r="645" ht="14.25" customHeight="1"/>
-    <row r="646" ht="14.25" customHeight="1"/>
-    <row r="647" ht="14.25" customHeight="1"/>
-    <row r="648" ht="14.25" customHeight="1"/>
-    <row r="649" ht="14.25" customHeight="1"/>
-    <row r="650" ht="14.25" customHeight="1"/>
-    <row r="651" ht="14.25" customHeight="1"/>
-    <row r="652" ht="14.25" customHeight="1"/>
-    <row r="653" ht="14.25" customHeight="1"/>
-    <row r="654" ht="14.25" customHeight="1"/>
-    <row r="655" ht="14.25" customHeight="1"/>
-    <row r="656" ht="14.25" customHeight="1"/>
-    <row r="657" ht="14.25" customHeight="1"/>
-    <row r="658" ht="14.25" customHeight="1"/>
-    <row r="659" ht="14.25" customHeight="1"/>
-    <row r="660" ht="14.25" customHeight="1"/>
-    <row r="661" ht="14.25" customHeight="1"/>
-    <row r="662" ht="14.25" customHeight="1"/>
-    <row r="663" ht="14.25" customHeight="1"/>
-    <row r="664" ht="14.25" customHeight="1"/>
-    <row r="665" ht="14.25" customHeight="1"/>
-    <row r="666" ht="14.25" customHeight="1"/>
-    <row r="667" ht="14.25" customHeight="1"/>
-    <row r="668" ht="14.25" customHeight="1"/>
-    <row r="669" ht="14.25" customHeight="1"/>
-    <row r="670" ht="14.25" customHeight="1"/>
-    <row r="671" ht="14.25" customHeight="1"/>
-    <row r="672" ht="14.25" customHeight="1"/>
-    <row r="673" ht="14.25" customHeight="1"/>
-    <row r="674" ht="14.25" customHeight="1"/>
-    <row r="675" ht="14.25" customHeight="1"/>
-    <row r="676" ht="14.25" customHeight="1"/>
-    <row r="677" ht="14.25" customHeight="1"/>
-    <row r="678" ht="14.25" customHeight="1"/>
-    <row r="679" ht="14.25" customHeight="1"/>
-    <row r="680" ht="14.25" customHeight="1"/>
-    <row r="681" ht="14.25" customHeight="1"/>
-    <row r="682" ht="14.25" customHeight="1"/>
-    <row r="683" ht="14.25" customHeight="1"/>
-    <row r="684" ht="14.25" customHeight="1"/>
-    <row r="685" ht="14.25" customHeight="1"/>
-    <row r="686" ht="14.25" customHeight="1"/>
-    <row r="687" ht="14.25" customHeight="1"/>
-    <row r="688" ht="14.25" customHeight="1"/>
-    <row r="689" ht="14.25" customHeight="1"/>
-    <row r="690" ht="14.25" customHeight="1"/>
-    <row r="691" ht="14.25" customHeight="1"/>
-    <row r="692" ht="14.25" customHeight="1"/>
-    <row r="693" ht="14.25" customHeight="1"/>
-    <row r="694" ht="14.25" customHeight="1"/>
-    <row r="695" ht="14.25" customHeight="1"/>
-    <row r="696" ht="14.25" customHeight="1"/>
-    <row r="697" ht="14.25" customHeight="1"/>
-    <row r="698" ht="14.25" customHeight="1"/>
-    <row r="699" ht="14.25" customHeight="1"/>
-    <row r="700" ht="14.25" customHeight="1"/>
-    <row r="701" ht="14.25" customHeight="1"/>
-    <row r="702" ht="14.25" customHeight="1"/>
-    <row r="703" ht="14.25" customHeight="1"/>
-    <row r="704" ht="14.25" customHeight="1"/>
-    <row r="705" ht="14.25" customHeight="1"/>
-    <row r="706" ht="14.25" customHeight="1"/>
-    <row r="707" ht="14.25" customHeight="1"/>
-    <row r="708" ht="14.25" customHeight="1"/>
-    <row r="709" ht="14.25" customHeight="1"/>
-    <row r="710" ht="14.25" customHeight="1"/>
-    <row r="711" ht="14.25" customHeight="1"/>
-    <row r="712" ht="14.25" customHeight="1"/>
-    <row r="713" ht="14.25" customHeight="1"/>
-    <row r="714" ht="14.25" customHeight="1"/>
-    <row r="715" ht="14.25" customHeight="1"/>
-    <row r="716" ht="14.25" customHeight="1"/>
-    <row r="717" ht="14.25" customHeight="1"/>
-    <row r="718" ht="14.25" customHeight="1"/>
-    <row r="719" ht="14.25" customHeight="1"/>
-    <row r="720" ht="14.25" customHeight="1"/>
-    <row r="721" ht="14.25" customHeight="1"/>
-    <row r="722" ht="14.25" customHeight="1"/>
-    <row r="723" ht="14.25" customHeight="1"/>
-    <row r="724" ht="14.25" customHeight="1"/>
-    <row r="725" ht="14.25" customHeight="1"/>
-    <row r="726" ht="14.25" customHeight="1"/>
-    <row r="727" ht="14.25" customHeight="1"/>
-    <row r="728" ht="14.25" customHeight="1"/>
-    <row r="729" ht="14.25" customHeight="1"/>
-    <row r="730" ht="14.25" customHeight="1"/>
-    <row r="731" ht="14.25" customHeight="1"/>
-    <row r="732" ht="14.25" customHeight="1"/>
-    <row r="733" ht="14.25" customHeight="1"/>
-    <row r="734" ht="14.25" customHeight="1"/>
-    <row r="735" ht="14.25" customHeight="1"/>
-    <row r="736" ht="14.25" customHeight="1"/>
-    <row r="737" ht="14.25" customHeight="1"/>
-    <row r="738" ht="14.25" customHeight="1"/>
-    <row r="739" ht="14.25" customHeight="1"/>
-    <row r="740" ht="14.25" customHeight="1"/>
-    <row r="741" ht="14.25" customHeight="1"/>
-    <row r="742" ht="14.25" customHeight="1"/>
-    <row r="743" ht="14.25" customHeight="1"/>
-    <row r="744" ht="14.25" customHeight="1"/>
-    <row r="745" ht="14.25" customHeight="1"/>
-    <row r="746" ht="14.25" customHeight="1"/>
-    <row r="747" ht="14.25" customHeight="1"/>
-    <row r="748" ht="14.25" customHeight="1"/>
-    <row r="749" ht="14.25" customHeight="1"/>
-    <row r="750" ht="14.25" customHeight="1"/>
-    <row r="751" ht="14.25" customHeight="1"/>
-    <row r="752" ht="14.25" customHeight="1"/>
-    <row r="753" ht="14.25" customHeight="1"/>
-    <row r="754" ht="14.25" customHeight="1"/>
-    <row r="755" ht="14.25" customHeight="1"/>
-    <row r="756" ht="14.25" customHeight="1"/>
-    <row r="757" ht="14.25" customHeight="1"/>
-    <row r="758" ht="14.25" customHeight="1"/>
-    <row r="759" ht="14.25" customHeight="1"/>
-    <row r="760" ht="14.25" customHeight="1"/>
-    <row r="761" ht="14.25" customHeight="1"/>
-    <row r="762" ht="14.25" customHeight="1"/>
-    <row r="763" ht="14.25" customHeight="1"/>
-    <row r="764" ht="14.25" customHeight="1"/>
-    <row r="765" ht="14.25" customHeight="1"/>
-    <row r="766" ht="14.25" customHeight="1"/>
-    <row r="767" ht="14.25" customHeight="1"/>
-    <row r="768" ht="14.25" customHeight="1"/>
-    <row r="769" ht="14.25" customHeight="1"/>
-    <row r="770" ht="14.25" customHeight="1"/>
-    <row r="771" ht="14.25" customHeight="1"/>
-    <row r="772" ht="14.25" customHeight="1"/>
-    <row r="773" ht="14.25" customHeight="1"/>
-    <row r="774" ht="14.25" customHeight="1"/>
-    <row r="775" ht="14.25" customHeight="1"/>
-    <row r="776" ht="14.25" customHeight="1"/>
-    <row r="777" ht="14.25" customHeight="1"/>
-    <row r="778" ht="14.25" customHeight="1"/>
-    <row r="779" ht="14.25" customHeight="1"/>
-    <row r="780" ht="14.25" customHeight="1"/>
-    <row r="781" ht="14.25" customHeight="1"/>
-    <row r="782" ht="14.25" customHeight="1"/>
-    <row r="783" ht="14.25" customHeight="1"/>
-    <row r="784" ht="14.25" customHeight="1"/>
-    <row r="785" ht="14.25" customHeight="1"/>
-    <row r="786" ht="14.25" customHeight="1"/>
-    <row r="787" ht="14.25" customHeight="1"/>
-    <row r="788" ht="14.25" customHeight="1"/>
-    <row r="789" ht="14.25" customHeight="1"/>
-    <row r="790" ht="14.25" customHeight="1"/>
-    <row r="791" ht="14.25" customHeight="1"/>
-    <row r="792" ht="14.25" customHeight="1"/>
-    <row r="793" ht="14.25" customHeight="1"/>
-    <row r="794" ht="14.25" customHeight="1"/>
-    <row r="795" ht="14.25" customHeight="1"/>
-    <row r="796" ht="14.25" customHeight="1"/>
-    <row r="797" ht="14.25" customHeight="1"/>
-    <row r="798" ht="14.25" customHeight="1"/>
-    <row r="799" ht="14.25" customHeight="1"/>
-    <row r="800" ht="14.25" customHeight="1"/>
-    <row r="801" ht="14.25" customHeight="1"/>
-    <row r="802" ht="14.25" customHeight="1"/>
-    <row r="803" ht="14.25" customHeight="1"/>
-    <row r="804" ht="14.25" customHeight="1"/>
-    <row r="805" ht="14.25" customHeight="1"/>
-    <row r="806" ht="14.25" customHeight="1"/>
-    <row r="807" ht="14.25" customHeight="1"/>
-    <row r="808" ht="14.25" customHeight="1"/>
-    <row r="809" ht="14.25" customHeight="1"/>
-    <row r="810" ht="14.25" customHeight="1"/>
-    <row r="811" ht="14.25" customHeight="1"/>
-    <row r="812" ht="14.25" customHeight="1"/>
-    <row r="813" ht="14.25" customHeight="1"/>
-    <row r="814" ht="14.25" customHeight="1"/>
-    <row r="815" ht="14.25" customHeight="1"/>
-    <row r="816" ht="14.25" customHeight="1"/>
-    <row r="817" ht="14.25" customHeight="1"/>
-    <row r="818" ht="14.25" customHeight="1"/>
-    <row r="819" ht="14.25" customHeight="1"/>
-    <row r="820" ht="14.25" customHeight="1"/>
-    <row r="821" ht="14.25" customHeight="1"/>
-    <row r="822" ht="14.25" customHeight="1"/>
-    <row r="823" ht="14.25" customHeight="1"/>
-    <row r="824" ht="14.25" customHeight="1"/>
-    <row r="825" ht="14.25" customHeight="1"/>
-    <row r="826" ht="14.25" customHeight="1"/>
-    <row r="827" ht="14.25" customHeight="1"/>
-    <row r="828" ht="14.25" customHeight="1"/>
-    <row r="829" ht="14.25" customHeight="1"/>
-    <row r="830" ht="14.25" customHeight="1"/>
-    <row r="831" ht="14.25" customHeight="1"/>
-    <row r="832" ht="14.25" customHeight="1"/>
-    <row r="833" ht="14.25" customHeight="1"/>
-    <row r="834" ht="14.25" customHeight="1"/>
-    <row r="835" ht="14.25" customHeight="1"/>
-    <row r="836" ht="14.25" customHeight="1"/>
-    <row r="837" ht="14.25" customHeight="1"/>
-    <row r="838" ht="14.25" customHeight="1"/>
-    <row r="839" ht="14.25" customHeight="1"/>
-    <row r="840" ht="14.25" customHeight="1"/>
-    <row r="841" ht="14.25" customHeight="1"/>
-    <row r="842" ht="14.25" customHeight="1"/>
-    <row r="843" ht="14.25" customHeight="1"/>
-    <row r="844" ht="14.25" customHeight="1"/>
-    <row r="845" ht="14.25" customHeight="1"/>
-    <row r="846" ht="14.25" customHeight="1"/>
-    <row r="847" ht="14.25" customHeight="1"/>
-    <row r="848" ht="14.25" customHeight="1"/>
-    <row r="849" ht="14.25" customHeight="1"/>
-    <row r="850" ht="14.25" customHeight="1"/>
-    <row r="851" ht="14.25" customHeight="1"/>
-    <row r="852" ht="14.25" customHeight="1"/>
-    <row r="853" ht="14.25" customHeight="1"/>
-    <row r="854" ht="14.25" customHeight="1"/>
-    <row r="855" ht="14.25" customHeight="1"/>
-    <row r="856" ht="14.25" customHeight="1"/>
-    <row r="857" ht="14.25" customHeight="1"/>
-    <row r="858" ht="14.25" customHeight="1"/>
-    <row r="859" ht="14.25" customHeight="1"/>
-    <row r="860" ht="14.25" customHeight="1"/>
-    <row r="861" ht="14.25" customHeight="1"/>
-    <row r="862" ht="14.25" customHeight="1"/>
-    <row r="863" ht="14.25" customHeight="1"/>
-    <row r="864" ht="14.25" customHeight="1"/>
-    <row r="865" ht="14.25" customHeight="1"/>
-    <row r="866" ht="14.25" customHeight="1"/>
-    <row r="867" ht="14.25" customHeight="1"/>
-    <row r="868" ht="14.25" customHeight="1"/>
-    <row r="869" ht="14.25" customHeight="1"/>
-    <row r="870" ht="14.25" customHeight="1"/>
-    <row r="871" ht="14.25" customHeight="1"/>
-    <row r="872" ht="14.25" customHeight="1"/>
-    <row r="873" ht="14.25" customHeight="1"/>
-    <row r="874" ht="14.25" customHeight="1"/>
-    <row r="875" ht="14.25" customHeight="1"/>
-    <row r="876" ht="14.25" customHeight="1"/>
-    <row r="877" ht="14.25" customHeight="1"/>
-    <row r="878" ht="14.25" customHeight="1"/>
-    <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-  </sheetData>
-  <phoneticPr fontId="2"/>
-  <hyperlinks>
-    <hyperlink ref="B27" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr codeName="Feuil1"/>
-  <dimension ref="A1:Z937"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" customWidth="1"/>
-    <col min="4" max="26" width="65.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-    </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1"/>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
+        <v>169</v>
+      </c>
+      <c r="B27" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -4461,6 +3165,1641 @@
     <row r="935" ht="14.25" customHeight="1"/>
     <row r="936" ht="14.25" customHeight="1"/>
     <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Feuil1"/>
+  <dimension ref="A1:Z998"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" customWidth="1"/>
+    <col min="4" max="26" width="65.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+    </row>
+    <row r="2" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="14.1" customHeight="1">
+      <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="14.1" customHeight="1">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A30" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A35" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A36" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" t="s">
+        <v>119</v>
+      </c>
+      <c r="C37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A40" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A41" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A42" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" t="s">
+        <v>135</v>
+      </c>
+      <c r="C42" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A43" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A44" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A45" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A46" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C46" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A47" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" t="s">
+        <v>141</v>
+      </c>
+      <c r="C48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A49" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" t="s">
+        <v>167</v>
+      </c>
+      <c r="C49" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A50" t="s">
+        <v>142</v>
+      </c>
+      <c r="B50" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="52" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="53" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="54" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="55" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="56" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="57" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="58" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="59" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="60" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="61" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="62" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="63" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="64" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+    <row r="971" ht="14.25" customHeight="1"/>
+    <row r="972" ht="14.25" customHeight="1"/>
+    <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
+    <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
+    <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
+    <row r="992" ht="14.25" customHeight="1"/>
+    <row r="993" ht="14.25" customHeight="1"/>
+    <row r="994" ht="14.25" customHeight="1"/>
+    <row r="995" ht="14.25" customHeight="1"/>
+    <row r="996" ht="14.25" customHeight="1"/>
+    <row r="997" ht="14.25" customHeight="1"/>
+    <row r="998" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="178">
   <si>
     <t>Name</t>
   </si>
@@ -536,14 +536,35 @@
     <t>NameZip</t>
   </si>
   <si>
-    <t>MATMUTRPA_RE7</t>
+    <t>Nom ZIP</t>
+  </si>
+  <si>
+    <t>DestinataireTechnique</t>
+  </si>
+  <si>
+    <t>BE017</t>
+  </si>
+  <si>
+    <t>Le fichier PDF ne contient pas de texte (image)</t>
+  </si>
+  <si>
+    <t>BE017Corps</t>
+  </si>
+  <si>
+    <t>bodyBE017</t>
+  </si>
+  <si>
+    <t>objectBE017</t>
+  </si>
+  <si>
+    <t>BE017Objet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -567,6 +588,11 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -588,7 +614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -596,6 +622,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -970,7 +999,9 @@
       <c r="A3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>168</v>
       </c>
@@ -2055,7 +2086,7 @@
         <v>31</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>39</v>
@@ -2252,7 +2283,7 @@
         <v>169</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
@@ -3205,7 +3236,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Feuil1"/>
-  <dimension ref="A1:Z998"/>
+  <dimension ref="A1:Z1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
@@ -3517,61 +3548,67 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A22" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>107</v>
       </c>
-      <c r="C21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>171</v>
       </c>
       <c r="C23" t="s">
         <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="14.25" customHeight="1">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
         <v>48</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="14.25" customHeight="1">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
         <v>48</v>
@@ -3579,10 +3616,10 @@
     </row>
     <row r="26" spans="1:4" ht="14.25" customHeight="1">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
         <v>48</v>
@@ -3590,10 +3627,10 @@
     </row>
     <row r="27" spans="1:4" ht="14.25" customHeight="1">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
         <v>48</v>
@@ -3601,10 +3638,10 @@
     </row>
     <row r="28" spans="1:4" ht="14.25" customHeight="1">
       <c r="A28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
         <v>48</v>
@@ -3612,10 +3649,10 @@
     </row>
     <row r="29" spans="1:4" ht="14.25" customHeight="1">
       <c r="A29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
         <v>48</v>
@@ -3623,10 +3660,10 @@
     </row>
     <row r="30" spans="1:4" ht="14.25" customHeight="1">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
         <v>48</v>
@@ -3634,10 +3671,10 @@
     </row>
     <row r="31" spans="1:4" ht="14.25" customHeight="1">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
         <v>48</v>
@@ -3645,186 +3682,189 @@
     </row>
     <row r="32" spans="1:4" ht="14.25" customHeight="1">
       <c r="A32" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A33" t="s">
         <v>102</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>115</v>
       </c>
-      <c r="C32" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A33" t="s">
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A34" t="s">
         <v>103</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>116</v>
       </c>
-      <c r="C33" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A34" t="s">
+      <c r="C34" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A35" t="s">
         <v>104</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>117</v>
       </c>
-      <c r="C34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A35" t="s">
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A36" t="s">
         <v>105</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>118</v>
       </c>
-      <c r="C35" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A36" t="s">
+      <c r="C36" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A37" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>165</v>
       </c>
-      <c r="C36" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A37" t="s">
+      <c r="C37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A38" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A39" t="s">
         <v>106</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B39" t="s">
         <v>119</v>
       </c>
-      <c r="C37" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A38" t="s">
+      <c r="C39" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A40" t="s">
         <v>120</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B40" t="s">
         <v>131</v>
       </c>
-      <c r="C38" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A39" t="s">
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A41" t="s">
         <v>121</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B41" t="s">
         <v>132</v>
       </c>
-      <c r="C39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A40" t="s">
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A42" t="s">
         <v>122</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B42" t="s">
         <v>133</v>
       </c>
-      <c r="C40" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A41" t="s">
+      <c r="C42" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A43" t="s">
         <v>123</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B43" t="s">
         <v>134</v>
       </c>
-      <c r="C41" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A42" t="s">
+      <c r="C43" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A44" t="s">
         <v>124</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B44" t="s">
         <v>135</v>
       </c>
-      <c r="C42" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A43" t="s">
+      <c r="C44" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A45" t="s">
         <v>125</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B45" t="s">
         <v>136</v>
       </c>
-      <c r="C43" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A44" t="s">
+      <c r="C45" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A46" t="s">
         <v>126</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B46" t="s">
         <v>137</v>
       </c>
-      <c r="C44" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A45" t="s">
+      <c r="C46" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A47" t="s">
         <v>127</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B47" t="s">
         <v>138</v>
       </c>
-      <c r="C45" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A46" t="s">
+      <c r="C47" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A48" t="s">
         <v>128</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B48" t="s">
         <v>139</v>
-      </c>
-      <c r="C46" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A47" t="s">
-        <v>129</v>
-      </c>
-      <c r="B47" t="s">
-        <v>140</v>
-      </c>
-      <c r="C47" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A48" t="s">
-        <v>130</v>
-      </c>
-      <c r="B48" t="s">
-        <v>141</v>
       </c>
       <c r="C48" t="s">
         <v>48</v>
@@ -3832,10 +3872,10 @@
     </row>
     <row r="49" spans="1:3" ht="14.25" customHeight="1">
       <c r="A49" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="B49" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="C49" t="s">
         <v>48</v>
@@ -3843,20 +3883,70 @@
     </row>
     <row r="50" spans="1:3" ht="14.25" customHeight="1">
       <c r="A50" t="s">
+        <v>130</v>
+      </c>
+      <c r="B50" t="s">
+        <v>141</v>
+      </c>
+      <c r="C50" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A51" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" t="s">
+        <v>167</v>
+      </c>
+      <c r="C51" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A52" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A53" t="s">
         <v>142</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B53" t="s">
         <v>143</v>
       </c>
-      <c r="C50" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="52" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="53" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="54" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="55" spans="1:3" ht="14.25" customHeight="1"/>
+      <c r="C53" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A54" t="s">
+        <v>153</v>
+      </c>
+      <c r="B54" t="s">
+        <v>153</v>
+      </c>
+      <c r="C54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A55" t="s">
+        <v>169</v>
+      </c>
+      <c r="B55" t="s">
+        <v>170</v>
+      </c>
+      <c r="C55" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="57" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="58" spans="1:3" ht="14.25" customHeight="1"/>
@@ -4800,6 +4890,9 @@
     <row r="996" ht="14.25" customHeight="1"/>
     <row r="997" ht="14.25" customHeight="1"/>
     <row r="998" ht="14.25" customHeight="1"/>
+    <row r="999" ht="14.25" customHeight="1"/>
+    <row r="1000" ht="14.25" customHeight="1"/>
+    <row r="1001" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="179">
   <si>
     <t>Name</t>
   </si>
@@ -558,6 +558,9 @@
   </si>
   <si>
     <t>BE017Objet</t>
+  </si>
+  <si>
+    <t>MaxFiles</t>
   </si>
 </sst>
 </file>
@@ -2286,7 +2289,14 @@
         <v>154</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A28" t="s">
+        <v>178</v>
+      </c>
+      <c r="B28">
+        <v>1000</v>
+      </c>
+    </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="30" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="31" spans="1:3" ht="14.25" customHeight="1"/>
